--- a/docs/survey/plateloop-survey-analysis.xlsx
+++ b/docs/survey/plateloop-survey-analysis.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\8jiwo\Downloads\plateloop\docs\survey\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CCB6B683-5734-4878-AAEA-EB4369D0AD4F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CC11ED4F-C306-4294-81FE-8C7E52D2CF9F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -272,14 +272,11 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="946" uniqueCount="401">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="943" uniqueCount="398">
   <si>
     <t>PlateLoop survey · results at a glance</t>
   </si>
   <si>
-    <t>Illustrative data: sample responses created to show how the analysis works, not collected from real people.</t>
-  </si>
-  <si>
     <t>responses in total</t>
   </si>
   <si>
@@ -382,7 +379,7 @@
     <t>Key findings</t>
   </si>
   <si>
-    <t>Calculated live from the responses. Illustrative data: sample responses created to show how the analysis works, not collected from real people.</t>
+    <t>Calculated live from the responses.</t>
   </si>
   <si>
     <t>Group</t>
@@ -1441,12 +1438,6 @@
     <t>About this workbook</t>
   </si>
   <si>
-    <t>Illustrative data</t>
-  </si>
-  <si>
-    <t>The responses are sample answers generated with a fixed seed (35) to show how the analysis works. They were not collected from real people. Replace them with real responses before drawing conclusions.</t>
-  </si>
-  <si>
     <t>Dashboard</t>
   </si>
   <si>
@@ -1465,7 +1456,7 @@
     <t>Data sheets</t>
   </si>
   <si>
-    <t>One row per respondent (blue text = input). To use real data, paste responses into these tables (same columns, up to row 1000) — every other sheet updates.</t>
+    <t>One row per respondent (blue text = input). To add responses, paste them into these tables (same columns, up to row 1000) — every other sheet updates.</t>
   </si>
   <si>
     <t>All questions, codes and answer options. Online version: https://8jiwoo.github.io/plateloop/survey/</t>
@@ -1645,12 +1636,6 @@
       <name val="Arial"/>
     </font>
     <font>
-      <i/>
-      <sz val="9"/>
-      <color rgb="FF8A938E"/>
-      <name val="Arial"/>
-    </font>
-    <font>
       <b/>
       <sz val="26"/>
       <color rgb="FFFFFFFF"/>
@@ -1671,6 +1656,12 @@
       <b/>
       <sz val="22"/>
       <color rgb="FF1B2420"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="9"/>
+      <color rgb="FF8A938E"/>
       <name val="Arial"/>
     </font>
     <font>
@@ -1983,7 +1974,7 @@
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="30" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="29" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
@@ -1993,7 +1984,7 @@
     <xf numFmtId="0" fontId="21" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="29" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -2006,11 +1997,11 @@
     <xf numFmtId="1" fontId="24" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="29" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="29" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="28" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="11" borderId="0" xfId="0" applyFill="1"/>
@@ -2020,7 +2011,7 @@
     <xf numFmtId="9" fontId="23" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="27" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -2029,17 +2020,14 @@
     <xf numFmtId="0" fontId="14" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="27" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="9" fontId="24" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="27" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -2051,19 +2039,22 @@
     <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="29" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="27" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="27" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="31" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2253,7 +2244,7 @@
               </c14:invertSolidFillFmt>
             </c:ext>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-7A89-4B5F-B518-5E84CE625C1F}"/>
+              <c16:uniqueId val="{00000000-CAD3-453E-835F-A6E7CB43B6F6}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -2442,7 +2433,7 @@
               </c14:invertSolidFillFmt>
             </c:ext>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-96DF-47C9-A886-73FCBBD0F9F7}"/>
+              <c16:uniqueId val="{00000000-89A9-42C6-B64A-06810F681058}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -2602,7 +2593,7 @@
               </c14:invertSolidFillFmt>
             </c:ext>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-0BBA-4BA2-B6EB-858CF92B776A}"/>
+              <c16:uniqueId val="{00000000-A7C1-44F7-B25A-660C2E374923}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -2785,7 +2776,7 @@
               </c14:invertSolidFillFmt>
             </c:ext>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-2CAD-4EB0-96E8-250BF7698701}"/>
+              <c16:uniqueId val="{00000000-C8F6-4505-A8D3-298FFE710500}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -2957,7 +2948,7 @@
               </c14:invertSolidFillFmt>
             </c:ext>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-ED4B-4141-B280-99904A1C9F62}"/>
+              <c16:uniqueId val="{00000000-B32E-4FAC-89A0-C84E7243A5B1}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -3129,7 +3120,7 @@
               </c14:invertSolidFillFmt>
             </c:ext>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-A089-4D4F-A4A2-34D275D4F0AA}"/>
+              <c16:uniqueId val="{00000000-A14F-45C3-9D74-BC2FF5183625}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -3295,7 +3286,7 @@
               </c14:invertSolidFillFmt>
             </c:ext>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-DA8F-4564-A4CB-D2DFBDA24E41}"/>
+              <c16:uniqueId val="{00000000-A6B9-4DAB-951D-9954009551DF}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -3467,7 +3458,7 @@
               </c14:invertSolidFillFmt>
             </c:ext>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-5F3F-42BC-B9A6-3CFF9223402A}"/>
+              <c16:uniqueId val="{00000000-A458-44A0-98FE-B145DAA1496A}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -3662,7 +3653,7 @@
               </c14:invertSolidFillFmt>
             </c:ext>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-58EE-4C3E-BC28-54DAAA9C3C53}"/>
+              <c16:uniqueId val="{00000000-2BFB-4ECF-A071-BAE1770886CC}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -3834,7 +3825,7 @@
               </c14:invertSolidFillFmt>
             </c:ext>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-07B4-48C0-AC5E-164CA548F2CE}"/>
+              <c16:uniqueId val="{00000000-415E-4033-A474-4AD7C8FF8B93}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -4023,7 +4014,7 @@
               </c14:invertSolidFillFmt>
             </c:ext>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-5ACD-4D32-8418-82A5011F0D09}"/>
+              <c16:uniqueId val="{00000000-8853-41C0-9F1C-156C122C3601}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -4189,7 +4180,7 @@
               </c14:invertSolidFillFmt>
             </c:ext>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-C567-4E24-926A-4995EA485816}"/>
+              <c16:uniqueId val="{00000000-751C-46A4-8B0F-7D0EA94F3DD9}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -4943,7 +4934,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:17" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B1" s="96" t="s">
+      <c r="B1" s="95" t="s">
         <v>0</v>
       </c>
       <c r="C1" s="70"/>
@@ -4962,26 +4953,7 @@
       <c r="P1" s="70"/>
       <c r="Q1" s="70"/>
     </row>
-    <row r="2" spans="2:17" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B2" s="92" t="s">
-        <v>1</v>
-      </c>
-      <c r="C2" s="70"/>
-      <c r="D2" s="70"/>
-      <c r="E2" s="70"/>
-      <c r="F2" s="70"/>
-      <c r="G2" s="70"/>
-      <c r="H2" s="70"/>
-      <c r="I2" s="70"/>
-      <c r="J2" s="70"/>
-      <c r="K2" s="70"/>
-      <c r="L2" s="70"/>
-      <c r="M2" s="70"/>
-      <c r="N2" s="70"/>
-      <c r="O2" s="70"/>
-      <c r="P2" s="70"/>
-      <c r="Q2" s="70"/>
-    </row>
+    <row r="2" spans="2:17" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="4" spans="2:17" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B4" s="89">
         <f>COUNTA(Students_Data!$A$2:$A$1000)+COUNTA(Kitchen_Data!$A$2:$A$1000)+COUNTA(Hospital_Data!$A$2:$A$1000)+COUNTA(Office_Data!$A$2:$A$1000)</f>
@@ -4989,13 +4961,13 @@
       </c>
       <c r="C4" s="83"/>
       <c r="D4" s="83"/>
-      <c r="E4" s="99">
+      <c r="E4" s="98">
         <f>COUNTA(Students_Data!$A$2:$A$1000)</f>
         <v>30</v>
       </c>
-      <c r="F4" s="94"/>
-      <c r="G4" s="94"/>
-      <c r="H4" s="98">
+      <c r="F4" s="93"/>
+      <c r="G4" s="93"/>
+      <c r="H4" s="97">
         <f>COUNTA(Kitchen_Data!$A$2:$A$1000)</f>
         <v>8</v>
       </c>
@@ -5016,54 +4988,54 @@
     </row>
     <row r="5" spans="2:17" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B5" s="82" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C5" s="83"/>
       <c r="D5" s="83"/>
-      <c r="E5" s="93" t="s">
+      <c r="E5" s="92" t="s">
+        <v>2</v>
+      </c>
+      <c r="F5" s="93"/>
+      <c r="G5" s="93"/>
+      <c r="H5" s="87" t="s">
         <v>3</v>
-      </c>
-      <c r="F5" s="94"/>
-      <c r="G5" s="94"/>
-      <c r="H5" s="87" t="s">
-        <v>4</v>
       </c>
       <c r="I5" s="81"/>
       <c r="J5" s="81"/>
-      <c r="K5" s="95" t="s">
-        <v>5</v>
+      <c r="K5" s="94" t="s">
+        <v>4</v>
       </c>
       <c r="L5" s="72"/>
       <c r="M5" s="72"/>
       <c r="N5" s="65" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="O5" s="66"/>
       <c r="P5" s="66"/>
     </row>
     <row r="8" spans="2:17" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B8" s="97" t="s">
-        <v>7</v>
-      </c>
-      <c r="C8" s="94"/>
-      <c r="D8" s="94"/>
-      <c r="E8" s="94"/>
-      <c r="F8" s="94"/>
-      <c r="G8" s="94"/>
-      <c r="H8" s="94"/>
-      <c r="I8" s="94"/>
-      <c r="J8" s="94"/>
-      <c r="K8" s="94"/>
-      <c r="L8" s="94"/>
-      <c r="M8" s="94"/>
-      <c r="N8" s="94"/>
-      <c r="O8" s="94"/>
-      <c r="P8" s="94"/>
-      <c r="Q8" s="94"/>
+      <c r="B8" s="96" t="s">
+        <v>6</v>
+      </c>
+      <c r="C8" s="93"/>
+      <c r="D8" s="93"/>
+      <c r="E8" s="93"/>
+      <c r="F8" s="93"/>
+      <c r="G8" s="93"/>
+      <c r="H8" s="93"/>
+      <c r="I8" s="93"/>
+      <c r="J8" s="93"/>
+      <c r="K8" s="93"/>
+      <c r="L8" s="93"/>
+      <c r="M8" s="93"/>
+      <c r="N8" s="93"/>
+      <c r="O8" s="93"/>
+      <c r="P8" s="93"/>
+      <c r="Q8" s="93"/>
     </row>
     <row r="9" spans="2:17" x14ac:dyDescent="0.25">
       <c r="N9" s="5" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="10" spans="2:17" ht="44.1" customHeight="1" x14ac:dyDescent="0.25">
@@ -5094,29 +5066,29 @@
     </row>
     <row r="11" spans="2:17" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B11" s="60" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C11" s="61"/>
       <c r="D11" s="61"/>
       <c r="E11" s="60" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F11" s="61"/>
       <c r="G11" s="61"/>
       <c r="H11" s="60" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="I11" s="61"/>
       <c r="J11" s="61"/>
       <c r="K11" s="60" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="L11" s="61"/>
       <c r="M11" s="61"/>
     </row>
     <row r="13" spans="2:17" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B13" s="69" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C13" s="70"/>
       <c r="D13" s="70"/>
@@ -5132,7 +5104,7 @@
     </row>
     <row r="16" spans="2:17" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B16" s="80" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C16" s="81"/>
       <c r="D16" s="81"/>
@@ -5152,7 +5124,7 @@
     </row>
     <row r="17" spans="2:17" x14ac:dyDescent="0.25">
       <c r="N17" s="6" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="18" spans="2:17" ht="44.1" customHeight="1" x14ac:dyDescent="0.25">
@@ -5183,29 +5155,29 @@
     </row>
     <row r="19" spans="2:17" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B19" s="63" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C19" s="64"/>
       <c r="D19" s="64"/>
       <c r="E19" s="63" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="F19" s="64"/>
       <c r="G19" s="64"/>
       <c r="H19" s="63" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="I19" s="64"/>
       <c r="J19" s="64"/>
       <c r="K19" s="63" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="L19" s="64"/>
       <c r="M19" s="64"/>
     </row>
     <row r="21" spans="2:17" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B21" s="100" t="s">
-        <v>20</v>
+      <c r="B21" s="99" t="s">
+        <v>19</v>
       </c>
       <c r="C21" s="70"/>
       <c r="D21" s="70"/>
@@ -5221,7 +5193,7 @@
     </row>
     <row r="24" spans="2:17" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B24" s="71" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C24" s="72"/>
       <c r="D24" s="72"/>
@@ -5241,7 +5213,7 @@
     </row>
     <row r="25" spans="2:17" x14ac:dyDescent="0.25">
       <c r="N25" s="7" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="26" spans="2:17" ht="44.1" customHeight="1" x14ac:dyDescent="0.25">
@@ -5272,29 +5244,29 @@
     </row>
     <row r="27" spans="2:17" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B27" s="76" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C27" s="77"/>
       <c r="D27" s="77"/>
       <c r="E27" s="76" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F27" s="77"/>
       <c r="G27" s="77"/>
       <c r="H27" s="76" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="I27" s="77"/>
       <c r="J27" s="77"/>
       <c r="K27" s="76" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="L27" s="77"/>
       <c r="M27" s="77"/>
     </row>
     <row r="29" spans="2:17" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B29" s="73" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C29" s="70"/>
       <c r="D29" s="70"/>
@@ -5310,7 +5282,7 @@
     </row>
     <row r="32" spans="2:17" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B32" s="75" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C32" s="66"/>
       <c r="D32" s="66"/>
@@ -5330,7 +5302,7 @@
     </row>
     <row r="33" spans="2:14" x14ac:dyDescent="0.25">
       <c r="N33" s="8" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="34" spans="2:14" ht="44.1" customHeight="1" x14ac:dyDescent="0.25">
@@ -5361,29 +5333,29 @@
     </row>
     <row r="35" spans="2:14" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B35" s="88" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C35" s="68"/>
       <c r="D35" s="68"/>
       <c r="E35" s="88" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F35" s="68"/>
       <c r="G35" s="68"/>
       <c r="H35" s="88" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I35" s="68"/>
       <c r="J35" s="68"/>
       <c r="K35" s="88" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="L35" s="68"/>
       <c r="M35" s="68"/>
     </row>
     <row r="37" spans="2:14" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B37" s="78" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C37" s="70"/>
       <c r="D37" s="70"/>
@@ -5398,7 +5370,7 @@
       <c r="M37" s="70"/>
     </row>
   </sheetData>
-  <mergeCells count="52">
+  <mergeCells count="51">
     <mergeCell ref="B1:Q1"/>
     <mergeCell ref="B8:Q8"/>
     <mergeCell ref="H4:J4"/>
@@ -5409,7 +5381,6 @@
     <mergeCell ref="B21:M21"/>
     <mergeCell ref="K11:M11"/>
     <mergeCell ref="N4:P4"/>
-    <mergeCell ref="B2:Q2"/>
     <mergeCell ref="H26:J26"/>
     <mergeCell ref="K34:M34"/>
     <mergeCell ref="H10:J10"/>
@@ -5479,247 +5450,247 @@
   <sheetData>
     <row r="1" spans="1:11" ht="72.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="51" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="B1" s="51" t="s">
+        <v>256</v>
+      </c>
+      <c r="C1" s="51" t="s">
         <v>257</v>
       </c>
-      <c r="C1" s="51" t="s">
+      <c r="D1" s="51" t="s">
         <v>258</v>
       </c>
-      <c r="D1" s="51" t="s">
+      <c r="E1" s="51" t="s">
         <v>259</v>
       </c>
-      <c r="E1" s="51" t="s">
+      <c r="F1" s="51" t="s">
         <v>260</v>
       </c>
-      <c r="F1" s="51" t="s">
+      <c r="G1" s="51" t="s">
         <v>261</v>
       </c>
-      <c r="G1" s="51" t="s">
+      <c r="H1" s="51" t="s">
         <v>262</v>
       </c>
-      <c r="H1" s="51" t="s">
+      <c r="I1" s="51" t="s">
         <v>263</v>
       </c>
-      <c r="I1" s="51" t="s">
+      <c r="J1" s="51" t="s">
         <v>264</v>
       </c>
-      <c r="J1" s="51" t="s">
+      <c r="K1" s="51" t="s">
         <v>265</v>
-      </c>
-      <c r="K1" s="51" t="s">
-        <v>266</v>
       </c>
     </row>
     <row r="2" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="45" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="B2" s="46" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="C2" s="45">
         <v>5</v>
       </c>
       <c r="D2" s="46" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="E2" s="45">
         <v>4</v>
       </c>
       <c r="F2" s="46" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="G2" s="46" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="H2" s="45">
         <v>5</v>
       </c>
       <c r="I2" s="46" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="J2" s="45">
         <v>8</v>
       </c>
       <c r="K2" s="46" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
     </row>
     <row r="3" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="47" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="B3" s="48" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="C3" s="47">
         <v>2</v>
       </c>
       <c r="D3" s="48" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="E3" s="47">
         <v>4</v>
       </c>
       <c r="F3" s="48" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="G3" s="48" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="H3" s="47">
         <v>5</v>
       </c>
       <c r="I3" s="48" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="J3" s="47">
         <v>14</v>
       </c>
       <c r="K3" s="48" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
     </row>
     <row r="4" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="45" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="B4" s="46" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="C4" s="45">
         <v>4</v>
       </c>
       <c r="D4" s="46" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="E4" s="45">
         <v>2</v>
       </c>
       <c r="F4" s="46" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="G4" s="46" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="H4" s="45">
         <v>3</v>
       </c>
       <c r="I4" s="46" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="J4" s="45">
         <v>2</v>
       </c>
       <c r="K4" s="46" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
     </row>
     <row r="5" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="47" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="B5" s="48" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="C5" s="47">
         <v>5</v>
       </c>
       <c r="D5" s="48" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="E5" s="47">
         <v>1</v>
       </c>
       <c r="F5" s="48" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="G5" s="48" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="H5" s="47">
         <v>4</v>
       </c>
       <c r="I5" s="48" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="J5" s="47">
         <v>7</v>
       </c>
       <c r="K5" s="48" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
     </row>
     <row r="6" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="45" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="B6" s="46" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="C6" s="45">
         <v>4</v>
       </c>
       <c r="D6" s="46" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="E6" s="45">
         <v>1</v>
       </c>
       <c r="F6" s="46" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="G6" s="46" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="H6" s="45">
         <v>4</v>
       </c>
       <c r="I6" s="46" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="J6" s="45">
         <v>12</v>
       </c>
       <c r="K6" s="46" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
     </row>
     <row r="7" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="47" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="B7" s="48" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="C7" s="47">
         <v>4</v>
       </c>
       <c r="D7" s="48" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="E7" s="47">
         <v>3</v>
       </c>
       <c r="F7" s="48" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="G7" s="48" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="H7" s="47">
         <v>1</v>
       </c>
       <c r="I7" s="48" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="J7" s="47">
         <v>16</v>
       </c>
       <c r="K7" s="48" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
     </row>
   </sheetData>
@@ -5768,7 +5739,7 @@
   <sheetData>
     <row r="1" spans="2:6" ht="32.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B1" s="121" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="C1" s="70"/>
       <c r="D1" s="70"/>
@@ -5777,733 +5748,733 @@
     </row>
     <row r="3" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B3" s="52" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C3" s="52" t="s">
+        <v>277</v>
+      </c>
+      <c r="D3" s="52" t="s">
         <v>278</v>
       </c>
-      <c r="D3" s="52" t="s">
+      <c r="E3" s="52" t="s">
         <v>279</v>
       </c>
-      <c r="E3" s="52" t="s">
+      <c r="F3" s="52" t="s">
         <v>280</v>
-      </c>
-      <c r="F3" s="52" t="s">
-        <v>281</v>
       </c>
     </row>
     <row r="4" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B4" s="53" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C4" s="54" t="s">
+        <v>281</v>
+      </c>
+      <c r="D4" s="54" t="s">
         <v>282</v>
       </c>
-      <c r="D4" s="54" t="s">
+      <c r="E4" s="54" t="s">
         <v>283</v>
       </c>
-      <c r="E4" s="54" t="s">
+      <c r="F4" s="54" t="s">
         <v>284</v>
-      </c>
-      <c r="F4" s="54" t="s">
-        <v>285</v>
       </c>
     </row>
     <row r="5" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B5" s="53" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C5" s="54" t="s">
+        <v>285</v>
+      </c>
+      <c r="D5" s="54" t="s">
         <v>286</v>
       </c>
-      <c r="D5" s="54" t="s">
+      <c r="E5" s="54" t="s">
+        <v>283</v>
+      </c>
+      <c r="F5" s="54" t="s">
         <v>287</v>
-      </c>
-      <c r="E5" s="54" t="s">
-        <v>284</v>
-      </c>
-      <c r="F5" s="54" t="s">
-        <v>288</v>
       </c>
     </row>
     <row r="6" spans="2:6" ht="25.5" x14ac:dyDescent="0.25">
       <c r="B6" s="53" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C6" s="54" t="s">
+        <v>288</v>
+      </c>
+      <c r="D6" s="54" t="s">
         <v>289</v>
       </c>
-      <c r="D6" s="54" t="s">
+      <c r="E6" s="54" t="s">
+        <v>283</v>
+      </c>
+      <c r="F6" s="54" t="s">
         <v>290</v>
-      </c>
-      <c r="E6" s="54" t="s">
-        <v>284</v>
-      </c>
-      <c r="F6" s="54" t="s">
-        <v>291</v>
       </c>
     </row>
     <row r="7" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B7" s="53" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C7" s="54" t="s">
+        <v>291</v>
+      </c>
+      <c r="D7" s="54" t="s">
         <v>292</v>
       </c>
-      <c r="D7" s="54" t="s">
+      <c r="E7" s="54" t="s">
+        <v>283</v>
+      </c>
+      <c r="F7" s="54" t="s">
         <v>293</v>
-      </c>
-      <c r="E7" s="54" t="s">
-        <v>284</v>
-      </c>
-      <c r="F7" s="54" t="s">
-        <v>294</v>
       </c>
     </row>
     <row r="8" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B8" s="53" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C8" s="54" t="s">
+        <v>294</v>
+      </c>
+      <c r="D8" s="54" t="s">
         <v>295</v>
       </c>
-      <c r="D8" s="54" t="s">
+      <c r="E8" s="54" t="s">
+        <v>283</v>
+      </c>
+      <c r="F8" s="54" t="s">
         <v>296</v>
-      </c>
-      <c r="E8" s="54" t="s">
-        <v>284</v>
-      </c>
-      <c r="F8" s="54" t="s">
-        <v>297</v>
       </c>
     </row>
     <row r="9" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B9" s="53" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C9" s="54" t="s">
+        <v>297</v>
+      </c>
+      <c r="D9" s="54" t="s">
         <v>298</v>
       </c>
-      <c r="D9" s="54" t="s">
+      <c r="E9" s="54" t="s">
         <v>299</v>
       </c>
-      <c r="E9" s="54" t="s">
+      <c r="F9" s="54" t="s">
         <v>300</v>
-      </c>
-      <c r="F9" s="54" t="s">
-        <v>301</v>
       </c>
     </row>
     <row r="10" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B10" s="53" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C10" s="54" t="s">
+        <v>301</v>
+      </c>
+      <c r="D10" s="54" t="s">
         <v>302</v>
       </c>
-      <c r="D10" s="54" t="s">
+      <c r="E10" s="54" t="s">
+        <v>283</v>
+      </c>
+      <c r="F10" s="54" t="s">
         <v>303</v>
-      </c>
-      <c r="E10" s="54" t="s">
-        <v>284</v>
-      </c>
-      <c r="F10" s="54" t="s">
-        <v>304</v>
       </c>
     </row>
     <row r="11" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B11" s="53" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C11" s="54" t="s">
+        <v>304</v>
+      </c>
+      <c r="D11" s="54" t="s">
         <v>305</v>
       </c>
-      <c r="D11" s="54" t="s">
-        <v>306</v>
-      </c>
       <c r="E11" s="54" t="s">
+        <v>299</v>
+      </c>
+      <c r="F11" s="54" t="s">
         <v>300</v>
-      </c>
-      <c r="F11" s="54" t="s">
-        <v>301</v>
       </c>
     </row>
     <row r="12" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B12" s="53" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C12" s="54" t="s">
+        <v>306</v>
+      </c>
+      <c r="D12" s="54" t="s">
         <v>307</v>
       </c>
-      <c r="D12" s="54" t="s">
-        <v>308</v>
-      </c>
       <c r="E12" s="54" t="s">
+        <v>299</v>
+      </c>
+      <c r="F12" s="54" t="s">
         <v>300</v>
-      </c>
-      <c r="F12" s="54" t="s">
-        <v>301</v>
       </c>
     </row>
     <row r="13" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B13" s="53" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C13" s="54" t="s">
+        <v>308</v>
+      </c>
+      <c r="D13" s="54" t="s">
         <v>309</v>
       </c>
-      <c r="D13" s="54" t="s">
-        <v>310</v>
-      </c>
       <c r="E13" s="54" t="s">
+        <v>299</v>
+      </c>
+      <c r="F13" s="54" t="s">
         <v>300</v>
-      </c>
-      <c r="F13" s="54" t="s">
-        <v>301</v>
       </c>
     </row>
     <row r="14" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B14" s="53" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C14" s="54" t="s">
+        <v>310</v>
+      </c>
+      <c r="D14" s="54" t="s">
         <v>311</v>
       </c>
-      <c r="D14" s="54" t="s">
+      <c r="E14" s="54" t="s">
         <v>312</v>
       </c>
-      <c r="E14" s="54" t="s">
+      <c r="F14" s="54" t="s">
         <v>313</v>
-      </c>
-      <c r="F14" s="54" t="s">
-        <v>314</v>
       </c>
     </row>
     <row r="15" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B15" s="55" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C15" s="54" t="s">
+        <v>314</v>
+      </c>
+      <c r="D15" s="54" t="s">
         <v>315</v>
       </c>
-      <c r="D15" s="54" t="s">
+      <c r="E15" s="54" t="s">
+        <v>283</v>
+      </c>
+      <c r="F15" s="54" t="s">
         <v>316</v>
-      </c>
-      <c r="E15" s="54" t="s">
-        <v>284</v>
-      </c>
-      <c r="F15" s="54" t="s">
-        <v>317</v>
       </c>
     </row>
     <row r="16" spans="2:6" ht="25.5" x14ac:dyDescent="0.25">
       <c r="B16" s="55" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C16" s="54" t="s">
+        <v>317</v>
+      </c>
+      <c r="D16" s="54" t="s">
         <v>318</v>
       </c>
-      <c r="D16" s="54" t="s">
+      <c r="E16" s="54" t="s">
+        <v>283</v>
+      </c>
+      <c r="F16" s="54" t="s">
         <v>319</v>
-      </c>
-      <c r="E16" s="54" t="s">
-        <v>284</v>
-      </c>
-      <c r="F16" s="54" t="s">
-        <v>320</v>
       </c>
     </row>
     <row r="17" spans="2:6" ht="25.5" x14ac:dyDescent="0.25">
       <c r="B17" s="55" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C17" s="54" t="s">
+        <v>320</v>
+      </c>
+      <c r="D17" s="54" t="s">
         <v>321</v>
       </c>
-      <c r="D17" s="54" t="s">
+      <c r="E17" s="54" t="s">
         <v>322</v>
       </c>
-      <c r="E17" s="54" t="s">
-        <v>323</v>
-      </c>
       <c r="F17" s="54" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
     </row>
     <row r="18" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B18" s="55" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C18" s="54" t="s">
+        <v>323</v>
+      </c>
+      <c r="D18" s="54" t="s">
         <v>324</v>
       </c>
-      <c r="D18" s="54" t="s">
+      <c r="E18" s="54" t="s">
+        <v>283</v>
+      </c>
+      <c r="F18" s="54" t="s">
         <v>325</v>
-      </c>
-      <c r="E18" s="54" t="s">
-        <v>284</v>
-      </c>
-      <c r="F18" s="54" t="s">
-        <v>326</v>
       </c>
     </row>
     <row r="19" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B19" s="55" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C19" s="54" t="s">
+        <v>326</v>
+      </c>
+      <c r="D19" s="54" t="s">
         <v>327</v>
       </c>
-      <c r="D19" s="54" t="s">
+      <c r="E19" s="54" t="s">
+        <v>283</v>
+      </c>
+      <c r="F19" s="54" t="s">
         <v>328</v>
-      </c>
-      <c r="E19" s="54" t="s">
-        <v>284</v>
-      </c>
-      <c r="F19" s="54" t="s">
-        <v>329</v>
       </c>
     </row>
     <row r="20" spans="2:6" ht="25.5" x14ac:dyDescent="0.25">
       <c r="B20" s="55" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C20" s="54" t="s">
+        <v>329</v>
+      </c>
+      <c r="D20" s="54" t="s">
         <v>330</v>
       </c>
-      <c r="D20" s="54" t="s">
+      <c r="E20" s="54" t="s">
+        <v>299</v>
+      </c>
+      <c r="F20" s="54" t="s">
         <v>331</v>
-      </c>
-      <c r="E20" s="54" t="s">
-        <v>300</v>
-      </c>
-      <c r="F20" s="54" t="s">
-        <v>332</v>
       </c>
     </row>
     <row r="21" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B21" s="55" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C21" s="54" t="s">
+        <v>332</v>
+      </c>
+      <c r="D21" s="54" t="s">
         <v>333</v>
       </c>
-      <c r="D21" s="54" t="s">
-        <v>334</v>
-      </c>
       <c r="E21" s="54" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="F21" s="54" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
     </row>
     <row r="22" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B22" s="55" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C22" s="54" t="s">
+        <v>334</v>
+      </c>
+      <c r="D22" s="54" t="s">
         <v>335</v>
       </c>
-      <c r="D22" s="54" t="s">
-        <v>336</v>
-      </c>
       <c r="E22" s="54" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="F22" s="54" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
     </row>
     <row r="23" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B23" s="55" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C23" s="54" t="s">
+        <v>336</v>
+      </c>
+      <c r="D23" s="54" t="s">
         <v>337</v>
       </c>
-      <c r="D23" s="54" t="s">
-        <v>338</v>
-      </c>
       <c r="E23" s="54" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="F23" s="54" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
     </row>
     <row r="24" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B24" s="55" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C24" s="54" t="s">
+        <v>338</v>
+      </c>
+      <c r="D24" s="54" t="s">
         <v>339</v>
       </c>
-      <c r="D24" s="54" t="s">
-        <v>340</v>
-      </c>
       <c r="E24" s="54" t="s">
+        <v>299</v>
+      </c>
+      <c r="F24" s="54" t="s">
         <v>300</v>
-      </c>
-      <c r="F24" s="54" t="s">
-        <v>301</v>
       </c>
     </row>
     <row r="25" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B25" s="55" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C25" s="54" t="s">
+        <v>340</v>
+      </c>
+      <c r="D25" s="54" t="s">
         <v>341</v>
       </c>
-      <c r="D25" s="54" t="s">
-        <v>342</v>
-      </c>
       <c r="E25" s="54" t="s">
+        <v>312</v>
+      </c>
+      <c r="F25" s="54" t="s">
         <v>313</v>
-      </c>
-      <c r="F25" s="54" t="s">
-        <v>314</v>
       </c>
     </row>
     <row r="26" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B26" s="56" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C26" s="54" t="s">
+        <v>342</v>
+      </c>
+      <c r="D26" s="54" t="s">
+        <v>315</v>
+      </c>
+      <c r="E26" s="54" t="s">
+        <v>283</v>
+      </c>
+      <c r="F26" s="54" t="s">
         <v>343</v>
-      </c>
-      <c r="D26" s="54" t="s">
-        <v>316</v>
-      </c>
-      <c r="E26" s="54" t="s">
-        <v>284</v>
-      </c>
-      <c r="F26" s="54" t="s">
-        <v>344</v>
       </c>
     </row>
     <row r="27" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B27" s="56" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C27" s="54" t="s">
+        <v>344</v>
+      </c>
+      <c r="D27" s="54" t="s">
         <v>345</v>
       </c>
-      <c r="D27" s="54" t="s">
+      <c r="E27" s="54" t="s">
+        <v>283</v>
+      </c>
+      <c r="F27" s="54" t="s">
         <v>346</v>
-      </c>
-      <c r="E27" s="54" t="s">
-        <v>284</v>
-      </c>
-      <c r="F27" s="54" t="s">
-        <v>347</v>
       </c>
     </row>
     <row r="28" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B28" s="56" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C28" s="54" t="s">
+        <v>347</v>
+      </c>
+      <c r="D28" s="54" t="s">
         <v>348</v>
       </c>
-      <c r="D28" s="54" t="s">
-        <v>349</v>
-      </c>
       <c r="E28" s="54" t="s">
+        <v>299</v>
+      </c>
+      <c r="F28" s="54" t="s">
         <v>300</v>
-      </c>
-      <c r="F28" s="54" t="s">
-        <v>301</v>
       </c>
     </row>
     <row r="29" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B29" s="56" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C29" s="54" t="s">
+        <v>349</v>
+      </c>
+      <c r="D29" s="54" t="s">
         <v>350</v>
       </c>
-      <c r="D29" s="54" t="s">
-        <v>351</v>
-      </c>
       <c r="E29" s="54" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="F29" s="54" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
     </row>
     <row r="30" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B30" s="56" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C30" s="54" t="s">
+        <v>351</v>
+      </c>
+      <c r="D30" s="54" t="s">
         <v>352</v>
       </c>
-      <c r="D30" s="54" t="s">
+      <c r="E30" s="54" t="s">
+        <v>283</v>
+      </c>
+      <c r="F30" s="54" t="s">
         <v>353</v>
-      </c>
-      <c r="E30" s="54" t="s">
-        <v>284</v>
-      </c>
-      <c r="F30" s="54" t="s">
-        <v>354</v>
       </c>
     </row>
     <row r="31" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B31" s="56" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C31" s="54" t="s">
+        <v>354</v>
+      </c>
+      <c r="D31" s="54" t="s">
         <v>355</v>
       </c>
-      <c r="D31" s="54" t="s">
+      <c r="E31" s="54" t="s">
+        <v>283</v>
+      </c>
+      <c r="F31" s="54" t="s">
         <v>356</v>
-      </c>
-      <c r="E31" s="54" t="s">
-        <v>284</v>
-      </c>
-      <c r="F31" s="54" t="s">
-        <v>357</v>
       </c>
     </row>
     <row r="32" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B32" s="56" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C32" s="54" t="s">
+        <v>357</v>
+      </c>
+      <c r="D32" s="54" t="s">
         <v>358</v>
       </c>
-      <c r="D32" s="54" t="s">
-        <v>359</v>
-      </c>
       <c r="E32" s="54" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="F32" s="54" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
     </row>
     <row r="33" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B33" s="56" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C33" s="54" t="s">
+        <v>359</v>
+      </c>
+      <c r="D33" s="54" t="s">
         <v>360</v>
       </c>
-      <c r="D33" s="54" t="s">
-        <v>361</v>
-      </c>
       <c r="E33" s="54" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="F33" s="54" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
     </row>
     <row r="34" spans="2:6" ht="25.5" x14ac:dyDescent="0.25">
       <c r="B34" s="56" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C34" s="54" t="s">
+        <v>361</v>
+      </c>
+      <c r="D34" s="54" t="s">
         <v>362</v>
       </c>
-      <c r="D34" s="54" t="s">
-        <v>363</v>
-      </c>
       <c r="E34" s="54" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="F34" s="54" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
     </row>
     <row r="35" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B35" s="56" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C35" s="54" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="D35" s="54" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="E35" s="54" t="s">
+        <v>312</v>
+      </c>
+      <c r="F35" s="54" t="s">
         <v>313</v>
-      </c>
-      <c r="F35" s="54" t="s">
-        <v>314</v>
       </c>
     </row>
     <row r="36" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B36" s="57" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C36" s="54" t="s">
+        <v>364</v>
+      </c>
+      <c r="D36" s="54" t="s">
         <v>365</v>
       </c>
-      <c r="D36" s="54" t="s">
+      <c r="E36" s="54" t="s">
+        <v>283</v>
+      </c>
+      <c r="F36" s="54" t="s">
         <v>366</v>
-      </c>
-      <c r="E36" s="54" t="s">
-        <v>284</v>
-      </c>
-      <c r="F36" s="54" t="s">
-        <v>367</v>
       </c>
     </row>
     <row r="37" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B37" s="57" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C37" s="54" t="s">
+        <v>367</v>
+      </c>
+      <c r="D37" s="54" t="s">
         <v>368</v>
       </c>
-      <c r="D37" s="54" t="s">
-        <v>369</v>
-      </c>
       <c r="E37" s="54" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="F37" s="54" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
     </row>
     <row r="38" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B38" s="57" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C38" s="54" t="s">
+        <v>369</v>
+      </c>
+      <c r="D38" s="54" t="s">
         <v>370</v>
       </c>
-      <c r="D38" s="54" t="s">
+      <c r="E38" s="54" t="s">
+        <v>283</v>
+      </c>
+      <c r="F38" s="54" t="s">
         <v>371</v>
-      </c>
-      <c r="E38" s="54" t="s">
-        <v>284</v>
-      </c>
-      <c r="F38" s="54" t="s">
-        <v>372</v>
       </c>
     </row>
     <row r="39" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B39" s="57" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C39" s="54" t="s">
+        <v>372</v>
+      </c>
+      <c r="D39" s="54" t="s">
         <v>373</v>
       </c>
-      <c r="D39" s="54" t="s">
-        <v>374</v>
-      </c>
       <c r="E39" s="54" t="s">
+        <v>299</v>
+      </c>
+      <c r="F39" s="54" t="s">
         <v>300</v>
-      </c>
-      <c r="F39" s="54" t="s">
-        <v>301</v>
       </c>
     </row>
     <row r="40" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B40" s="57" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C40" s="54" t="s">
+        <v>374</v>
+      </c>
+      <c r="D40" s="54" t="s">
         <v>375</v>
       </c>
-      <c r="D40" s="54" t="s">
+      <c r="E40" s="54" t="s">
+        <v>283</v>
+      </c>
+      <c r="F40" s="54" t="s">
         <v>376</v>
-      </c>
-      <c r="E40" s="54" t="s">
-        <v>284</v>
-      </c>
-      <c r="F40" s="54" t="s">
-        <v>377</v>
       </c>
     </row>
     <row r="41" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B41" s="57" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C41" s="54" t="s">
+        <v>377</v>
+      </c>
+      <c r="D41" s="54" t="s">
         <v>378</v>
       </c>
-      <c r="D41" s="54" t="s">
-        <v>379</v>
-      </c>
       <c r="E41" s="54" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="F41" s="54" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
     </row>
     <row r="42" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B42" s="57" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C42" s="54" t="s">
+        <v>379</v>
+      </c>
+      <c r="D42" s="54" t="s">
         <v>380</v>
       </c>
-      <c r="D42" s="54" t="s">
-        <v>381</v>
-      </c>
       <c r="E42" s="54" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="F42" s="54" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
     </row>
     <row r="43" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B43" s="57" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C43" s="54" t="s">
+        <v>381</v>
+      </c>
+      <c r="D43" s="54" t="s">
         <v>382</v>
       </c>
-      <c r="D43" s="54" t="s">
+      <c r="E43" s="54" t="s">
+        <v>283</v>
+      </c>
+      <c r="F43" s="54" t="s">
         <v>383</v>
-      </c>
-      <c r="E43" s="54" t="s">
-        <v>284</v>
-      </c>
-      <c r="F43" s="54" t="s">
-        <v>384</v>
       </c>
     </row>
     <row r="44" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B44" s="57" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C44" s="54" t="s">
+        <v>384</v>
+      </c>
+      <c r="D44" s="54" t="s">
         <v>385</v>
       </c>
-      <c r="D44" s="54" t="s">
-        <v>386</v>
-      </c>
       <c r="E44" s="54" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="F44" s="54" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
     </row>
     <row r="45" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B45" s="57" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C45" s="54" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="D45" s="54" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="E45" s="54" t="s">
+        <v>312</v>
+      </c>
+      <c r="F45" s="54" t="s">
         <v>313</v>
-      </c>
-      <c r="F45" s="54" t="s">
-        <v>314</v>
       </c>
     </row>
   </sheetData>
@@ -6516,7 +6487,7 @@
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0B00-000000000000}">
-  <dimension ref="B1:C9"/>
+  <dimension ref="B1:C8"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="2" customWidth="1"/>
@@ -6526,64 +6497,56 @@
   <sheetData>
     <row r="1" spans="2:3" ht="32.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B1" s="121" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="C1" s="70"/>
     </row>
     <row r="3" spans="2:3" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B3" s="58" t="s">
+        <v>388</v>
+      </c>
+      <c r="C3" s="59" t="s">
         <v>389</v>
-      </c>
-      <c r="C3" s="59" t="s">
-        <v>390</v>
       </c>
     </row>
     <row r="4" spans="2:3" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B4" s="58" t="s">
-        <v>391</v>
+        <v>34</v>
       </c>
       <c r="C4" s="59" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
     </row>
     <row r="5" spans="2:3" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B5" s="58" t="s">
-        <v>35</v>
+        <v>391</v>
       </c>
       <c r="C5" s="59" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
     </row>
     <row r="6" spans="2:3" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B6" s="58" t="s">
+        <v>393</v>
+      </c>
+      <c r="C6" s="59" t="s">
         <v>394</v>
-      </c>
-      <c r="C6" s="59" t="s">
-        <v>395</v>
       </c>
     </row>
     <row r="7" spans="2:3" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B7" s="58" t="s">
-        <v>396</v>
+        <v>276</v>
       </c>
       <c r="C7" s="59" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
     </row>
     <row r="8" spans="2:3" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B8" s="58" t="s">
-        <v>277</v>
+        <v>396</v>
       </c>
       <c r="C8" s="59" t="s">
-        <v>398</v>
-      </c>
-    </row>
-    <row r="9" spans="2:3" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B9" s="58" t="s">
-        <v>399</v>
-      </c>
-      <c r="C9" s="59" t="s">
-        <v>400</v>
+        <v>397</v>
       </c>
     </row>
   </sheetData>
@@ -6609,7 +6572,7 @@
   <sheetData>
     <row r="1" spans="2:6" ht="36" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B1" s="101" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C1" s="70"/>
       <c r="D1" s="70"/>
@@ -6617,8 +6580,8 @@
       <c r="F1" s="70"/>
     </row>
     <row r="2" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B2" s="92" t="s">
-        <v>36</v>
+      <c r="B2" s="100" t="s">
+        <v>35</v>
       </c>
       <c r="C2" s="70"/>
       <c r="D2" s="70"/>
@@ -6627,22 +6590,22 @@
     </row>
     <row r="4" spans="2:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B4" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="C4" s="9" t="s">
         <v>37</v>
-      </c>
-      <c r="C4" s="9" t="s">
-        <v>38</v>
       </c>
       <c r="D4" s="9"/>
       <c r="E4" s="9" t="s">
+        <v>38</v>
+      </c>
+      <c r="F4" s="9" t="s">
         <v>39</v>
-      </c>
-      <c r="F4" s="9" t="s">
-        <v>40</v>
       </c>
     </row>
     <row r="5" spans="2:6" ht="45.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B5" s="10" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C5" s="11">
         <f>MAX(Students!$F$25:$F$29)</f>
@@ -6657,12 +6620,12 @@
         <v>The most common reason for leaving food is 'Portion too big' (43%); 47% would take a smaller portion if they could ask easily.</v>
       </c>
       <c r="F5" s="14" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="6" spans="2:6" ht="45.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B6" s="10" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C6" s="11">
         <f>Students!$F$48</f>
@@ -6677,12 +6640,12 @@
         <v>When seeing what they ate, 57% would rather see food groups and 10% calories.</v>
       </c>
       <c r="F6" s="14" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="7" spans="2:6" ht="45.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B7" s="10" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C7" s="15">
         <f>Students!$F$57</f>
@@ -6697,12 +6660,12 @@
         <v>Interest in scanning trays to feed a virtual pet averages 4.0 out of 5; 67% agree.</v>
       </c>
       <c r="F7" s="14" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="8" spans="2:6" ht="45.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B8" s="10" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C8" s="11">
         <f>Students!$G$59</f>
@@ -6717,12 +6680,12 @@
         <v>43% of students are comfortable with face sign-in.</v>
       </c>
       <c r="F8" s="14" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="9" spans="2:6" ht="45.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B9" s="16" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C9" s="17">
         <f>Kitchen!$F$17+Kitchen!$F$18</f>
@@ -6737,12 +6700,12 @@
         <v>63% of kitchen staff decide quantities by experience or headcount; 13% know accurately which dishes come back.</v>
       </c>
       <c r="F9" s="20" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="10" spans="2:6" ht="45.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B10" s="16" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C10" s="17">
         <f>Kitchen!$B$24/100</f>
@@ -6757,12 +6720,12 @@
         <v>Kitchen staff estimate 22% of cooked food is thrown away and spend 32 minutes a day planning quantities.</v>
       </c>
       <c r="F10" s="20" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="11" spans="2:6" ht="45.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B11" s="16" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C11" s="17">
         <f>Kitchen!$G$50</f>
@@ -6777,12 +6740,12 @@
         <v>A suggested order is rated useful by 75% and waste by dish by 100%; 50% worry about extra workload.</v>
       </c>
       <c r="F11" s="20" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="12" spans="2:6" ht="45.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B12" s="21" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C12" s="22">
         <f>Hospital!$G$53</f>
@@ -6797,12 +6760,12 @@
         <v>17% of hospital staff trust their intake records; documenting intake takes 31 minutes a shift.</v>
       </c>
       <c r="F12" s="25" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="13" spans="2:6" ht="45.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B13" s="21" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C13" s="22">
         <f>Hospital!$F$29</f>
@@ -6817,12 +6780,12 @@
         <v>Staff say a patient who stops eating is noticed the same day in 33% of cases.</v>
       </c>
       <c r="F13" s="25" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="14" spans="2:6" ht="45.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B14" s="21" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C14" s="22">
         <f>Hospital!$G$54</f>
@@ -6837,12 +6800,12 @@
         <v>Automatic intake records are rated useful by 100%; 50% say patients would benefit from choosing tomorrow’s meals.</v>
       </c>
       <c r="F14" s="25" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="15" spans="2:6" ht="45.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B15" s="26" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C15" s="27">
         <f>Office!$F$34+Office!$F$35</f>
@@ -6857,12 +6820,12 @@
         <v>33% of office workers know the nutrients in their lunch; 50% feel an afternoon energy dip often or daily.</v>
       </c>
       <c r="F15" s="30" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="16" spans="2:6" ht="45.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B16" s="26" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C16" s="27">
         <f>Office!$F$40</f>
@@ -6877,12 +6840,12 @@
         <v>33% would pre-order lunch to skip a typical 10-minute queue.</v>
       </c>
       <c r="F16" s="30" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="17" spans="2:6" ht="45.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B17" s="26" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C17" s="27">
         <f>Office!$F$47</f>
@@ -6897,7 +6860,7 @@
         <v>17% would share meal data with their employer; 50% would share anonymous totals only.</v>
       </c>
       <c r="F17" s="30" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
   </sheetData>
@@ -7040,7 +7003,7 @@
   <sheetData>
     <row r="1" spans="2:15" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B1" s="111" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C1" s="70"/>
       <c r="D1" s="70"/>
@@ -7058,8 +7021,8 @@
     </row>
     <row r="2" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B2" s="31" t="str">
-        <f>COUNTA(Students_Data!$A$2:$A$1000)&amp;" responses · illustrative data · PlateLoop answer: Loopi"</f>
-        <v>30 responses · illustrative data · PlateLoop answer: Loopi</v>
+        <f>COUNTA(Students_Data!$A$2:$A$1000)&amp;" responses · PlateLoop answer: Loopi"</f>
+        <v>30 responses · PlateLoop answer: Loopi</v>
       </c>
     </row>
     <row r="4" spans="2:15" ht="44.1" customHeight="1" x14ac:dyDescent="0.25">
@@ -7090,29 +7053,29 @@
     </row>
     <row r="5" spans="2:15" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B5" s="60" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C5" s="61"/>
       <c r="D5" s="61"/>
       <c r="E5" s="60" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F5" s="61"/>
       <c r="G5" s="61"/>
       <c r="H5" s="60" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="I5" s="61"/>
       <c r="J5" s="61"/>
       <c r="K5" s="60" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="L5" s="61"/>
       <c r="M5" s="61"/>
     </row>
     <row r="8" spans="2:15" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B8" s="106" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C8" s="70"/>
       <c r="D8" s="70"/>
@@ -7123,22 +7086,22 @@
     </row>
     <row r="9" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B9" s="108" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C9" s="70"/>
       <c r="D9" s="70"/>
       <c r="E9" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="F9" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="F9" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="G9" s="93"/>
+      <c r="G9" s="92"/>
       <c r="H9" s="70"/>
     </row>
     <row r="10" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B10" s="104" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C10" s="105"/>
       <c r="D10" s="105"/>
@@ -7158,7 +7121,7 @@
     </row>
     <row r="11" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B11" s="102" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C11" s="103"/>
       <c r="D11" s="103"/>
@@ -7178,7 +7141,7 @@
     </row>
     <row r="14" spans="2:15" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B14" s="106" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C14" s="70"/>
       <c r="D14" s="70"/>
@@ -7189,22 +7152,22 @@
     </row>
     <row r="15" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B15" s="108" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C15" s="70"/>
       <c r="D15" s="70"/>
       <c r="E15" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="F15" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="F15" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="G15" s="93"/>
+      <c r="G15" s="92"/>
       <c r="H15" s="70"/>
     </row>
     <row r="16" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B16" s="104" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C16" s="105"/>
       <c r="D16" s="105"/>
@@ -7224,7 +7187,7 @@
     </row>
     <row r="17" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B17" s="102" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C17" s="103"/>
       <c r="D17" s="103"/>
@@ -7244,7 +7207,7 @@
     </row>
     <row r="18" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B18" s="104" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C18" s="105"/>
       <c r="D18" s="105"/>
@@ -7264,7 +7227,7 @@
     </row>
     <row r="19" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B19" s="102" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C19" s="103"/>
       <c r="D19" s="103"/>
@@ -7284,7 +7247,7 @@
     </row>
     <row r="20" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B20" s="104" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C20" s="105"/>
       <c r="D20" s="105"/>
@@ -7304,7 +7267,7 @@
     </row>
     <row r="23" spans="2:8" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B23" s="106" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C23" s="70"/>
       <c r="D23" s="70"/>
@@ -7315,22 +7278,22 @@
     </row>
     <row r="24" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B24" s="108" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C24" s="70"/>
       <c r="D24" s="70"/>
       <c r="E24" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="F24" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="F24" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="G24" s="93"/>
+      <c r="G24" s="92"/>
       <c r="H24" s="70"/>
     </row>
     <row r="25" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B25" s="104" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C25" s="105"/>
       <c r="D25" s="105"/>
@@ -7350,7 +7313,7 @@
     </row>
     <row r="26" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B26" s="102" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C26" s="103"/>
       <c r="D26" s="103"/>
@@ -7370,7 +7333,7 @@
     </row>
     <row r="27" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B27" s="104" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C27" s="105"/>
       <c r="D27" s="105"/>
@@ -7390,7 +7353,7 @@
     </row>
     <row r="28" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B28" s="102" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C28" s="103"/>
       <c r="D28" s="103"/>
@@ -7410,7 +7373,7 @@
     </row>
     <row r="29" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B29" s="104" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C29" s="105"/>
       <c r="D29" s="105"/>
@@ -7430,7 +7393,7 @@
     </row>
     <row r="32" spans="2:8" ht="32.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B32" s="106" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C32" s="70"/>
       <c r="D32" s="70"/>
@@ -7441,22 +7404,22 @@
     </row>
     <row r="33" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B33" s="108" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C33" s="70"/>
       <c r="D33" s="70"/>
       <c r="E33" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="F33" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="F33" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="G33" s="93"/>
+      <c r="G33" s="92"/>
       <c r="H33" s="70"/>
     </row>
     <row r="34" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B34" s="104" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C34" s="105"/>
       <c r="D34" s="105"/>
@@ -7476,7 +7439,7 @@
     </row>
     <row r="35" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B35" s="102" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C35" s="103"/>
       <c r="D35" s="103"/>
@@ -7496,7 +7459,7 @@
     </row>
     <row r="36" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B36" s="104" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C36" s="105"/>
       <c r="D36" s="105"/>
@@ -7516,7 +7479,7 @@
     </row>
     <row r="39" spans="2:8" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B39" s="106" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C39" s="70"/>
       <c r="D39" s="70"/>
@@ -7527,22 +7490,22 @@
     </row>
     <row r="40" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B40" s="108" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C40" s="70"/>
       <c r="D40" s="70"/>
       <c r="E40" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="F40" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="F40" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="G40" s="93"/>
+      <c r="G40" s="92"/>
       <c r="H40" s="70"/>
     </row>
     <row r="41" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B41" s="104" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C41" s="105"/>
       <c r="D41" s="105"/>
@@ -7562,7 +7525,7 @@
     </row>
     <row r="42" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B42" s="102" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C42" s="103"/>
       <c r="D42" s="103"/>
@@ -7582,7 +7545,7 @@
     </row>
     <row r="43" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B43" s="104" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C43" s="105"/>
       <c r="D43" s="105"/>
@@ -7602,7 +7565,7 @@
     </row>
     <row r="46" spans="2:8" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B46" s="106" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C46" s="70"/>
       <c r="D46" s="70"/>
@@ -7613,22 +7576,22 @@
     </row>
     <row r="47" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B47" s="108" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C47" s="70"/>
       <c r="D47" s="70"/>
       <c r="E47" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="F47" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="F47" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="G47" s="93"/>
+      <c r="G47" s="92"/>
       <c r="H47" s="70"/>
     </row>
     <row r="48" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B48" s="104" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C48" s="105"/>
       <c r="D48" s="105"/>
@@ -7648,7 +7611,7 @@
     </row>
     <row r="49" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B49" s="102" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C49" s="103"/>
       <c r="D49" s="103"/>
@@ -7668,7 +7631,7 @@
     </row>
     <row r="50" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B50" s="104" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C50" s="105"/>
       <c r="D50" s="105"/>
@@ -7688,7 +7651,7 @@
     </row>
     <row r="51" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B51" s="102" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C51" s="103"/>
       <c r="D51" s="103"/>
@@ -7708,7 +7671,7 @@
     </row>
     <row r="54" spans="2:8" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B54" s="106" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C54" s="70"/>
       <c r="D54" s="70"/>
@@ -7719,22 +7682,22 @@
     </row>
     <row r="55" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B55" s="108" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C55" s="70"/>
       <c r="D55" s="70"/>
       <c r="E55" s="70"/>
       <c r="F55" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="G55" s="1" t="s">
         <v>84</v>
-      </c>
-      <c r="G55" s="1" t="s">
-        <v>85</v>
       </c>
       <c r="H55" s="1"/>
     </row>
     <row r="56" spans="2:8" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B56" s="110" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C56" s="105"/>
       <c r="D56" s="105"/>
@@ -7754,7 +7717,7 @@
     </row>
     <row r="57" spans="2:8" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B57" s="110" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C57" s="105"/>
       <c r="D57" s="105"/>
@@ -7774,7 +7737,7 @@
     </row>
     <row r="58" spans="2:8" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B58" s="110" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C58" s="105"/>
       <c r="D58" s="105"/>
@@ -7794,7 +7757,7 @@
     </row>
     <row r="59" spans="2:8" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B59" s="110" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C59" s="105"/>
       <c r="D59" s="105"/>
@@ -7974,7 +7937,7 @@
   <sheetData>
     <row r="1" spans="2:15" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B1" s="114" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C1" s="70"/>
       <c r="D1" s="70"/>
@@ -7992,8 +7955,8 @@
     </row>
     <row r="2" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B2" s="31" t="str">
-        <f>COUNTA(Kitchen_Data!$A$2:$A$1000)&amp;" responses · illustrative data · PlateLoop answer: Kitchen dashboard"</f>
-        <v>8 responses · illustrative data · PlateLoop answer: Kitchen dashboard</v>
+        <f>COUNTA(Kitchen_Data!$A$2:$A$1000)&amp;" responses · PlateLoop answer: Kitchen dashboard"</f>
+        <v>8 responses · PlateLoop answer: Kitchen dashboard</v>
       </c>
     </row>
     <row r="4" spans="2:15" ht="44.1" customHeight="1" x14ac:dyDescent="0.25">
@@ -8024,29 +7987,29 @@
     </row>
     <row r="5" spans="2:15" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B5" s="63" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C5" s="64"/>
       <c r="D5" s="64"/>
       <c r="E5" s="63" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="F5" s="64"/>
       <c r="G5" s="64"/>
       <c r="H5" s="63" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="I5" s="64"/>
       <c r="J5" s="64"/>
       <c r="K5" s="63" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="L5" s="64"/>
       <c r="M5" s="64"/>
     </row>
     <row r="8" spans="2:15" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B8" s="106" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C8" s="70"/>
       <c r="D8" s="70"/>
@@ -8057,22 +8020,22 @@
     </row>
     <row r="9" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B9" s="113" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C9" s="70"/>
       <c r="D9" s="70"/>
       <c r="E9" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="F9" s="2" t="s">
         <v>56</v>
-      </c>
-      <c r="F9" s="2" t="s">
-        <v>57</v>
       </c>
       <c r="G9" s="87"/>
       <c r="H9" s="70"/>
     </row>
     <row r="10" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B10" s="104" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C10" s="105"/>
       <c r="D10" s="105"/>
@@ -8092,7 +8055,7 @@
     </row>
     <row r="11" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B11" s="102" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C11" s="103"/>
       <c r="D11" s="103"/>
@@ -8112,7 +8075,7 @@
     </row>
     <row r="12" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B12" s="104" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C12" s="105"/>
       <c r="D12" s="105"/>
@@ -8132,7 +8095,7 @@
     </row>
     <row r="15" spans="2:15" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B15" s="106" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C15" s="70"/>
       <c r="D15" s="70"/>
@@ -8143,22 +8106,22 @@
     </row>
     <row r="16" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B16" s="113" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C16" s="70"/>
       <c r="D16" s="70"/>
       <c r="E16" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="F16" s="2" t="s">
         <v>56</v>
-      </c>
-      <c r="F16" s="2" t="s">
-        <v>57</v>
       </c>
       <c r="G16" s="87"/>
       <c r="H16" s="70"/>
     </row>
     <row r="17" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B17" s="104" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C17" s="105"/>
       <c r="D17" s="105"/>
@@ -8178,7 +8141,7 @@
     </row>
     <row r="18" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B18" s="102" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C18" s="103"/>
       <c r="D18" s="103"/>
@@ -8198,7 +8161,7 @@
     </row>
     <row r="19" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B19" s="104" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C19" s="105"/>
       <c r="D19" s="105"/>
@@ -8218,7 +8181,7 @@
     </row>
     <row r="20" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B20" s="102" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C20" s="103"/>
       <c r="D20" s="103"/>
@@ -8238,7 +8201,7 @@
     </row>
     <row r="23" spans="2:9" ht="32.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B23" s="106" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C23" s="70"/>
       <c r="D23" s="70"/>
@@ -8271,25 +8234,25 @@
     </row>
     <row r="25" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B25" s="63" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C25" s="64"/>
       <c r="D25" s="63" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E25" s="64"/>
       <c r="F25" s="63" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="G25" s="64"/>
       <c r="H25" s="63" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="I25" s="64"/>
     </row>
     <row r="27" spans="2:9" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B27" s="106" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C27" s="70"/>
       <c r="D27" s="70"/>
@@ -8300,22 +8263,22 @@
     </row>
     <row r="28" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B28" s="113" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C28" s="70"/>
       <c r="D28" s="70"/>
       <c r="E28" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="F28" s="2" t="s">
         <v>56</v>
-      </c>
-      <c r="F28" s="2" t="s">
-        <v>57</v>
       </c>
       <c r="G28" s="87"/>
       <c r="H28" s="70"/>
     </row>
     <row r="29" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B29" s="104" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C29" s="105"/>
       <c r="D29" s="105"/>
@@ -8335,7 +8298,7 @@
     </row>
     <row r="30" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B30" s="102" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C30" s="103"/>
       <c r="D30" s="103"/>
@@ -8355,7 +8318,7 @@
     </row>
     <row r="31" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B31" s="104" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C31" s="105"/>
       <c r="D31" s="105"/>
@@ -8375,7 +8338,7 @@
     </row>
     <row r="34" spans="2:9" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B34" s="106" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C34" s="70"/>
       <c r="D34" s="70"/>
@@ -8386,22 +8349,22 @@
     </row>
     <row r="35" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B35" s="113" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C35" s="70"/>
       <c r="D35" s="70"/>
       <c r="E35" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="F35" s="2" t="s">
         <v>56</v>
-      </c>
-      <c r="F35" s="2" t="s">
-        <v>57</v>
       </c>
       <c r="G35" s="87"/>
       <c r="H35" s="70"/>
     </row>
     <row r="36" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B36" s="104" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C36" s="105"/>
       <c r="D36" s="105"/>
@@ -8421,7 +8384,7 @@
     </row>
     <row r="37" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B37" s="102" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C37" s="103"/>
       <c r="D37" s="103"/>
@@ -8441,7 +8404,7 @@
     </row>
     <row r="38" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B38" s="104" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C38" s="105"/>
       <c r="D38" s="105"/>
@@ -8461,7 +8424,7 @@
     </row>
     <row r="39" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B39" s="102" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C39" s="103"/>
       <c r="D39" s="103"/>
@@ -8481,7 +8444,7 @@
     </row>
     <row r="40" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B40" s="104" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C40" s="105"/>
       <c r="D40" s="105"/>
@@ -8501,7 +8464,7 @@
     </row>
     <row r="43" spans="2:9" ht="32.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B43" s="106" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C43" s="70"/>
       <c r="D43" s="70"/>
@@ -8534,25 +8497,25 @@
     </row>
     <row r="45" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B45" s="63" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C45" s="64"/>
       <c r="D45" s="63" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E45" s="64"/>
       <c r="F45" s="63" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="G45" s="64"/>
       <c r="H45" s="63" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="I45" s="64"/>
     </row>
     <row r="47" spans="2:9" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B47" s="106" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C47" s="70"/>
       <c r="D47" s="70"/>
@@ -8563,22 +8526,22 @@
     </row>
     <row r="48" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B48" s="113" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C48" s="70"/>
       <c r="D48" s="70"/>
       <c r="E48" s="70"/>
       <c r="F48" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="G48" s="2" t="s">
         <v>84</v>
-      </c>
-      <c r="G48" s="2" t="s">
-        <v>85</v>
       </c>
       <c r="H48" s="2"/>
     </row>
     <row r="49" spans="2:8" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B49" s="110" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="C49" s="105"/>
       <c r="D49" s="105"/>
@@ -8598,7 +8561,7 @@
     </row>
     <row r="50" spans="2:8" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B50" s="110" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="C50" s="105"/>
       <c r="D50" s="105"/>
@@ -8618,7 +8581,7 @@
     </row>
     <row r="51" spans="2:8" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B51" s="110" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C51" s="105"/>
       <c r="D51" s="105"/>
@@ -8638,7 +8601,7 @@
     </row>
     <row r="52" spans="2:8" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B52" s="110" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="C52" s="105"/>
       <c r="D52" s="105"/>
@@ -8798,7 +8761,7 @@
   <sheetData>
     <row r="1" spans="2:15" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B1" s="117" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C1" s="70"/>
       <c r="D1" s="70"/>
@@ -8816,8 +8779,8 @@
     </row>
     <row r="2" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B2" s="31" t="str">
-        <f>COUNTA(Hospital_Data!$A$2:$A$1000)&amp;" responses · illustrative data · PlateLoop answer: Loopi Care"</f>
-        <v>6 responses · illustrative data · PlateLoop answer: Loopi Care</v>
+        <f>COUNTA(Hospital_Data!$A$2:$A$1000)&amp;" responses · PlateLoop answer: Loopi Care"</f>
+        <v>6 responses · PlateLoop answer: Loopi Care</v>
       </c>
     </row>
     <row r="4" spans="2:15" ht="44.1" customHeight="1" x14ac:dyDescent="0.25">
@@ -8848,29 +8811,29 @@
     </row>
     <row r="5" spans="2:15" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B5" s="76" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C5" s="77"/>
       <c r="D5" s="77"/>
       <c r="E5" s="76" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F5" s="77"/>
       <c r="G5" s="77"/>
       <c r="H5" s="76" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="I5" s="77"/>
       <c r="J5" s="77"/>
       <c r="K5" s="76" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="L5" s="77"/>
       <c r="M5" s="77"/>
     </row>
     <row r="8" spans="2:15" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B8" s="106" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C8" s="70"/>
       <c r="D8" s="70"/>
@@ -8881,22 +8844,22 @@
     </row>
     <row r="9" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B9" s="115" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C9" s="70"/>
       <c r="D9" s="70"/>
       <c r="E9" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="F9" s="3" t="s">
         <v>56</v>
       </c>
-      <c r="F9" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="G9" s="95"/>
+      <c r="G9" s="94"/>
       <c r="H9" s="70"/>
     </row>
     <row r="10" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B10" s="104" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="C10" s="105"/>
       <c r="D10" s="105"/>
@@ -8916,7 +8879,7 @@
     </row>
     <row r="11" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B11" s="102" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C11" s="103"/>
       <c r="D11" s="103"/>
@@ -8936,7 +8899,7 @@
     </row>
     <row r="12" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B12" s="104" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="C12" s="105"/>
       <c r="D12" s="105"/>
@@ -8956,7 +8919,7 @@
     </row>
     <row r="15" spans="2:15" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B15" s="106" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="C15" s="70"/>
       <c r="D15" s="70"/>
@@ -8967,22 +8930,22 @@
     </row>
     <row r="16" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B16" s="115" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C16" s="70"/>
       <c r="D16" s="70"/>
       <c r="E16" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="F16" s="3" t="s">
         <v>56</v>
       </c>
-      <c r="F16" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="G16" s="95"/>
+      <c r="G16" s="94"/>
       <c r="H16" s="70"/>
     </row>
     <row r="17" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B17" s="104" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="C17" s="105"/>
       <c r="D17" s="105"/>
@@ -9002,7 +8965,7 @@
     </row>
     <row r="18" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B18" s="102" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="C18" s="103"/>
       <c r="D18" s="103"/>
@@ -9022,7 +8985,7 @@
     </row>
     <row r="19" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B19" s="104" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C19" s="105"/>
       <c r="D19" s="105"/>
@@ -9042,7 +9005,7 @@
     </row>
     <row r="20" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B20" s="102" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C20" s="103"/>
       <c r="D20" s="103"/>
@@ -9062,7 +9025,7 @@
     </row>
     <row r="23" spans="2:9" ht="32.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B23" s="106" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C23" s="70"/>
       <c r="D23" s="70"/>
@@ -9095,25 +9058,25 @@
     </row>
     <row r="25" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B25" s="76" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C25" s="77"/>
       <c r="D25" s="76" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E25" s="77"/>
       <c r="F25" s="76" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="G25" s="77"/>
       <c r="H25" s="76" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="I25" s="77"/>
     </row>
     <row r="27" spans="2:9" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B27" s="106" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C27" s="70"/>
       <c r="D27" s="70"/>
@@ -9124,22 +9087,22 @@
     </row>
     <row r="28" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B28" s="115" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C28" s="70"/>
       <c r="D28" s="70"/>
       <c r="E28" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="F28" s="3" t="s">
         <v>56</v>
       </c>
-      <c r="F28" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="G28" s="95"/>
+      <c r="G28" s="94"/>
       <c r="H28" s="70"/>
     </row>
     <row r="29" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B29" s="104" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C29" s="105"/>
       <c r="D29" s="105"/>
@@ -9159,7 +9122,7 @@
     </row>
     <row r="30" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B30" s="102" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="C30" s="103"/>
       <c r="D30" s="103"/>
@@ -9179,7 +9142,7 @@
     </row>
     <row r="31" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B31" s="104" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="C31" s="105"/>
       <c r="D31" s="105"/>
@@ -9199,7 +9162,7 @@
     </row>
     <row r="32" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B32" s="102" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="C32" s="103"/>
       <c r="D32" s="103"/>
@@ -9219,7 +9182,7 @@
     </row>
     <row r="35" spans="2:8" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B35" s="106" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C35" s="70"/>
       <c r="D35" s="70"/>
@@ -9230,22 +9193,22 @@
     </row>
     <row r="36" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B36" s="115" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C36" s="70"/>
       <c r="D36" s="70"/>
       <c r="E36" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="F36" s="3" t="s">
         <v>56</v>
       </c>
-      <c r="F36" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="G36" s="95"/>
+      <c r="G36" s="94"/>
       <c r="H36" s="70"/>
     </row>
     <row r="37" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B37" s="104" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="C37" s="105"/>
       <c r="D37" s="105"/>
@@ -9265,7 +9228,7 @@
     </row>
     <row r="38" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B38" s="102" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C38" s="103"/>
       <c r="D38" s="103"/>
@@ -9285,7 +9248,7 @@
     </row>
     <row r="39" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B39" s="104" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C39" s="105"/>
       <c r="D39" s="105"/>
@@ -9305,7 +9268,7 @@
     </row>
     <row r="40" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B40" s="102" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C40" s="103"/>
       <c r="D40" s="103"/>
@@ -9325,7 +9288,7 @@
     </row>
     <row r="41" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B41" s="104" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C41" s="105"/>
       <c r="D41" s="105"/>
@@ -9345,7 +9308,7 @@
     </row>
     <row r="44" spans="2:8" ht="32.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B44" s="106" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="C44" s="70"/>
       <c r="D44" s="70"/>
@@ -9356,22 +9319,22 @@
     </row>
     <row r="45" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B45" s="115" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C45" s="70"/>
       <c r="D45" s="70"/>
       <c r="E45" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="F45" s="3" t="s">
         <v>56</v>
       </c>
-      <c r="F45" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="G45" s="95"/>
+      <c r="G45" s="94"/>
       <c r="H45" s="70"/>
     </row>
     <row r="46" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B46" s="104" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C46" s="105"/>
       <c r="D46" s="105"/>
@@ -9391,7 +9354,7 @@
     </row>
     <row r="47" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B47" s="102" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C47" s="103"/>
       <c r="D47" s="103"/>
@@ -9411,7 +9374,7 @@
     </row>
     <row r="48" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B48" s="104" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C48" s="105"/>
       <c r="D48" s="105"/>
@@ -9431,7 +9394,7 @@
     </row>
     <row r="51" spans="2:8" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B51" s="106" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C51" s="70"/>
       <c r="D51" s="70"/>
@@ -9442,22 +9405,22 @@
     </row>
     <row r="52" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B52" s="115" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C52" s="70"/>
       <c r="D52" s="70"/>
       <c r="E52" s="70"/>
       <c r="F52" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="G52" s="3" t="s">
         <v>84</v>
-      </c>
-      <c r="G52" s="3" t="s">
-        <v>85</v>
       </c>
       <c r="H52" s="3"/>
     </row>
     <row r="53" spans="2:8" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B53" s="110" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="C53" s="105"/>
       <c r="D53" s="105"/>
@@ -9477,7 +9440,7 @@
     </row>
     <row r="54" spans="2:8" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B54" s="110" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="C54" s="105"/>
       <c r="D54" s="105"/>
@@ -9497,7 +9460,7 @@
     </row>
     <row r="55" spans="2:8" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B55" s="110" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="C55" s="105"/>
       <c r="D55" s="105"/>
@@ -9667,7 +9630,7 @@
   <sheetData>
     <row r="1" spans="2:15" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B1" s="120" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C1" s="70"/>
       <c r="D1" s="70"/>
@@ -9685,8 +9648,8 @@
     </row>
     <row r="2" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B2" s="31" t="str">
-        <f>COUNTA(Office_Data!$A$2:$A$1000)&amp;" responses · illustrative data · PlateLoop answer: Loopi Work"</f>
-        <v>6 responses · illustrative data · PlateLoop answer: Loopi Work</v>
+        <f>COUNTA(Office_Data!$A$2:$A$1000)&amp;" responses · PlateLoop answer: Loopi Work"</f>
+        <v>6 responses · PlateLoop answer: Loopi Work</v>
       </c>
     </row>
     <row r="4" spans="2:15" ht="44.1" customHeight="1" x14ac:dyDescent="0.25">
@@ -9717,29 +9680,29 @@
     </row>
     <row r="5" spans="2:15" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B5" s="88" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C5" s="68"/>
       <c r="D5" s="68"/>
       <c r="E5" s="88" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F5" s="68"/>
       <c r="G5" s="68"/>
       <c r="H5" s="88" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I5" s="68"/>
       <c r="J5" s="68"/>
       <c r="K5" s="88" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="L5" s="68"/>
       <c r="M5" s="68"/>
     </row>
     <row r="8" spans="2:15" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B8" s="106" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="C8" s="70"/>
       <c r="D8" s="70"/>
@@ -9750,22 +9713,22 @@
     </row>
     <row r="9" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B9" s="119" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C9" s="70"/>
       <c r="D9" s="70"/>
       <c r="E9" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="F9" s="4" t="s">
         <v>56</v>
-      </c>
-      <c r="F9" s="4" t="s">
-        <v>57</v>
       </c>
       <c r="G9" s="65"/>
       <c r="H9" s="70"/>
     </row>
     <row r="10" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B10" s="104" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="C10" s="105"/>
       <c r="D10" s="105"/>
@@ -9785,7 +9748,7 @@
     </row>
     <row r="11" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B11" s="102" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="C11" s="103"/>
       <c r="D11" s="103"/>
@@ -9805,7 +9768,7 @@
     </row>
     <row r="12" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B12" s="104" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="C12" s="105"/>
       <c r="D12" s="105"/>
@@ -9825,7 +9788,7 @@
     </row>
     <row r="13" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B13" s="102" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="C13" s="103"/>
       <c r="D13" s="103"/>
@@ -9845,7 +9808,7 @@
     </row>
     <row r="16" spans="2:15" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B16" s="106" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="C16" s="70"/>
       <c r="D16" s="70"/>
@@ -9878,25 +9841,25 @@
     </row>
     <row r="18" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B18" s="88" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C18" s="68"/>
       <c r="D18" s="88" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E18" s="68"/>
       <c r="F18" s="88" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="G18" s="68"/>
       <c r="H18" s="88" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="I18" s="68"/>
     </row>
     <row r="20" spans="2:9" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B20" s="106" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="C20" s="70"/>
       <c r="D20" s="70"/>
@@ -9907,22 +9870,22 @@
     </row>
     <row r="21" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B21" s="119" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C21" s="70"/>
       <c r="D21" s="70"/>
       <c r="E21" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="F21" s="4" t="s">
         <v>56</v>
-      </c>
-      <c r="F21" s="4" t="s">
-        <v>57</v>
       </c>
       <c r="G21" s="65"/>
       <c r="H21" s="70"/>
     </row>
     <row r="22" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B22" s="104" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C22" s="105"/>
       <c r="D22" s="105"/>
@@ -9942,7 +9905,7 @@
     </row>
     <row r="23" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B23" s="102" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C23" s="103"/>
       <c r="D23" s="103"/>
@@ -9962,7 +9925,7 @@
     </row>
     <row r="24" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B24" s="104" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="C24" s="105"/>
       <c r="D24" s="105"/>
@@ -9982,7 +9945,7 @@
     </row>
     <row r="25" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B25" s="102" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="C25" s="103"/>
       <c r="D25" s="103"/>
@@ -10002,7 +9965,7 @@
     </row>
     <row r="26" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B26" s="104" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="C26" s="105"/>
       <c r="D26" s="105"/>
@@ -10022,7 +9985,7 @@
     </row>
     <row r="29" spans="2:9" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B29" s="106" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="C29" s="70"/>
       <c r="D29" s="70"/>
@@ -10033,22 +9996,22 @@
     </row>
     <row r="30" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B30" s="119" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C30" s="70"/>
       <c r="D30" s="70"/>
       <c r="E30" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="F30" s="4" t="s">
         <v>56</v>
-      </c>
-      <c r="F30" s="4" t="s">
-        <v>57</v>
       </c>
       <c r="G30" s="65"/>
       <c r="H30" s="70"/>
     </row>
     <row r="31" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B31" s="104" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C31" s="105"/>
       <c r="D31" s="105"/>
@@ -10068,7 +10031,7 @@
     </row>
     <row r="32" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B32" s="102" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C32" s="103"/>
       <c r="D32" s="103"/>
@@ -10088,7 +10051,7 @@
     </row>
     <row r="33" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B33" s="104" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C33" s="105"/>
       <c r="D33" s="105"/>
@@ -10108,7 +10071,7 @@
     </row>
     <row r="34" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B34" s="102" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C34" s="103"/>
       <c r="D34" s="103"/>
@@ -10128,7 +10091,7 @@
     </row>
     <row r="35" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B35" s="104" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C35" s="105"/>
       <c r="D35" s="105"/>
@@ -10148,7 +10111,7 @@
     </row>
     <row r="38" spans="2:8" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B38" s="106" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="C38" s="70"/>
       <c r="D38" s="70"/>
@@ -10159,22 +10122,22 @@
     </row>
     <row r="39" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B39" s="119" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C39" s="70"/>
       <c r="D39" s="70"/>
       <c r="E39" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="F39" s="4" t="s">
         <v>56</v>
-      </c>
-      <c r="F39" s="4" t="s">
-        <v>57</v>
       </c>
       <c r="G39" s="65"/>
       <c r="H39" s="70"/>
     </row>
     <row r="40" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B40" s="104" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C40" s="105"/>
       <c r="D40" s="105"/>
@@ -10194,7 +10157,7 @@
     </row>
     <row r="41" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B41" s="102" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C41" s="103"/>
       <c r="D41" s="103"/>
@@ -10214,7 +10177,7 @@
     </row>
     <row r="42" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B42" s="104" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C42" s="105"/>
       <c r="D42" s="105"/>
@@ -10234,7 +10197,7 @@
     </row>
     <row r="45" spans="2:8" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B45" s="106" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C45" s="70"/>
       <c r="D45" s="70"/>
@@ -10245,22 +10208,22 @@
     </row>
     <row r="46" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B46" s="119" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C46" s="70"/>
       <c r="D46" s="70"/>
       <c r="E46" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="F46" s="4" t="s">
         <v>56</v>
-      </c>
-      <c r="F46" s="4" t="s">
-        <v>57</v>
       </c>
       <c r="G46" s="65"/>
       <c r="H46" s="70"/>
     </row>
     <row r="47" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B47" s="104" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C47" s="105"/>
       <c r="D47" s="105"/>
@@ -10280,7 +10243,7 @@
     </row>
     <row r="48" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B48" s="102" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="C48" s="103"/>
       <c r="D48" s="103"/>
@@ -10300,7 +10263,7 @@
     </row>
     <row r="49" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B49" s="104" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C49" s="105"/>
       <c r="D49" s="105"/>
@@ -10320,7 +10283,7 @@
     </row>
     <row r="52" spans="2:9" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B52" s="106" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="C52" s="70"/>
       <c r="D52" s="70"/>
@@ -10353,25 +10316,25 @@
     </row>
     <row r="54" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B54" s="88" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C54" s="68"/>
       <c r="D54" s="88" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E54" s="68"/>
       <c r="F54" s="88" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="G54" s="68"/>
       <c r="H54" s="88" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="I54" s="68"/>
     </row>
     <row r="56" spans="2:9" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B56" s="106" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C56" s="70"/>
       <c r="D56" s="70"/>
@@ -10382,22 +10345,22 @@
     </row>
     <row r="57" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B57" s="119" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C57" s="70"/>
       <c r="D57" s="70"/>
       <c r="E57" s="70"/>
       <c r="F57" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="G57" s="4" t="s">
         <v>84</v>
-      </c>
-      <c r="G57" s="4" t="s">
-        <v>85</v>
       </c>
       <c r="H57" s="4"/>
     </row>
     <row r="58" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B58" s="110" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="C58" s="105"/>
       <c r="D58" s="105"/>
@@ -10417,7 +10380,7 @@
     </row>
     <row r="59" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B59" s="110" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="C59" s="105"/>
       <c r="D59" s="105"/>
@@ -10601,66 +10564,66 @@
   <sheetData>
     <row r="1" spans="1:12" ht="86.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="44" t="s">
+        <v>157</v>
+      </c>
+      <c r="B1" s="44" t="s">
         <v>158</v>
       </c>
-      <c r="B1" s="44" t="s">
+      <c r="C1" s="44" t="s">
         <v>159</v>
       </c>
-      <c r="C1" s="44" t="s">
+      <c r="D1" s="44" t="s">
         <v>160</v>
       </c>
-      <c r="D1" s="44" t="s">
+      <c r="E1" s="44" t="s">
         <v>161</v>
       </c>
-      <c r="E1" s="44" t="s">
+      <c r="F1" s="44" t="s">
         <v>162</v>
       </c>
-      <c r="F1" s="44" t="s">
+      <c r="G1" s="44" t="s">
         <v>163</v>
       </c>
-      <c r="G1" s="44" t="s">
+      <c r="H1" s="44" t="s">
         <v>164</v>
       </c>
-      <c r="H1" s="44" t="s">
+      <c r="I1" s="44" t="s">
         <v>165</v>
       </c>
-      <c r="I1" s="44" t="s">
+      <c r="J1" s="44" t="s">
         <v>166</v>
       </c>
-      <c r="J1" s="44" t="s">
+      <c r="K1" s="44" t="s">
         <v>167</v>
       </c>
-      <c r="K1" s="44" t="s">
+      <c r="L1" s="44" t="s">
         <v>168</v>
-      </c>
-      <c r="L1" s="44" t="s">
-        <v>169</v>
       </c>
     </row>
     <row r="2" spans="1:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="45" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B2" s="46" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C2" s="46" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D2" s="46" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E2" s="46" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="F2" s="46" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="G2" s="45">
         <v>5</v>
       </c>
       <c r="H2" s="46" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="I2" s="45">
         <v>5</v>
@@ -10672,33 +10635,33 @@
         <v>5</v>
       </c>
       <c r="L2" s="46" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="3" spans="1:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="47" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="B3" s="48" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C3" s="48" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D3" s="48" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E3" s="48" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="F3" s="48" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="G3" s="47">
         <v>4</v>
       </c>
       <c r="H3" s="48" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="I3" s="47">
         <v>3</v>
@@ -10710,33 +10673,33 @@
         <v>3</v>
       </c>
       <c r="L3" s="48" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="4" spans="1:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="45" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="B4" s="46" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C4" s="46" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D4" s="46" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E4" s="46" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="F4" s="46" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="G4" s="45">
         <v>4</v>
       </c>
       <c r="H4" s="46" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="I4" s="45">
         <v>4</v>
@@ -10748,33 +10711,33 @@
         <v>4</v>
       </c>
       <c r="L4" s="46" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
     </row>
     <row r="5" spans="1:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="47" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="B5" s="48" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C5" s="48" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D5" s="48" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="E5" s="48" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="F5" s="48" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="G5" s="47">
         <v>4</v>
       </c>
       <c r="H5" s="48" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="I5" s="47">
         <v>3</v>
@@ -10786,33 +10749,33 @@
         <v>5</v>
       </c>
       <c r="L5" s="48" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
     </row>
     <row r="6" spans="1:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="45" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="B6" s="46" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C6" s="46" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D6" s="46" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E6" s="46" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="F6" s="46" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="G6" s="45">
         <v>4</v>
       </c>
       <c r="H6" s="46" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="I6" s="45">
         <v>4</v>
@@ -10824,33 +10787,33 @@
         <v>2</v>
       </c>
       <c r="L6" s="46" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
     </row>
     <row r="7" spans="1:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="47" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="B7" s="48" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C7" s="48" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D7" s="48" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E7" s="48" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="F7" s="48" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="G7" s="47">
         <v>3</v>
       </c>
       <c r="H7" s="48" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="I7" s="47">
         <v>5</v>
@@ -10862,33 +10825,33 @@
         <v>1</v>
       </c>
       <c r="L7" s="48" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
     </row>
     <row r="8" spans="1:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="45" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="B8" s="46" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C8" s="46" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D8" s="46" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E8" s="46" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="F8" s="46" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="G8" s="45">
         <v>3</v>
       </c>
       <c r="H8" s="46" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="I8" s="45">
         <v>3</v>
@@ -10900,33 +10863,33 @@
         <v>4</v>
       </c>
       <c r="L8" s="46" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
     </row>
     <row r="9" spans="1:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="47" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="B9" s="48" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C9" s="48" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D9" s="48" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E9" s="48" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="F9" s="48" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="G9" s="47">
         <v>5</v>
       </c>
       <c r="H9" s="48" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="I9" s="47">
         <v>4</v>
@@ -10938,33 +10901,33 @@
         <v>3</v>
       </c>
       <c r="L9" s="48" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
     </row>
     <row r="10" spans="1:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="45" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="B10" s="46" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C10" s="46" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D10" s="46" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E10" s="46" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="F10" s="46" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="G10" s="45">
         <v>4</v>
       </c>
       <c r="H10" s="46" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="I10" s="45">
         <v>3</v>
@@ -10976,33 +10939,33 @@
         <v>2</v>
       </c>
       <c r="L10" s="46" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
     </row>
     <row r="11" spans="1:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="47" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="B11" s="48" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C11" s="48" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D11" s="48" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E11" s="48" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="F11" s="48" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="G11" s="47">
         <v>4</v>
       </c>
       <c r="H11" s="48" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="I11" s="47">
         <v>5</v>
@@ -11014,33 +10977,33 @@
         <v>4</v>
       </c>
       <c r="L11" s="48" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
     </row>
     <row r="12" spans="1:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="45" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="B12" s="46" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C12" s="46" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D12" s="46" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E12" s="46" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="F12" s="46" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="G12" s="45">
         <v>4</v>
       </c>
       <c r="H12" s="46" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="I12" s="45">
         <v>5</v>
@@ -11052,33 +11015,33 @@
         <v>4</v>
       </c>
       <c r="L12" s="46" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
     </row>
     <row r="13" spans="1:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="47" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="B13" s="48" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C13" s="48" t="s">
+        <v>61</v>
+      </c>
+      <c r="D13" s="48" t="s">
+        <v>68</v>
+      </c>
+      <c r="E13" s="48" t="s">
+        <v>73</v>
+      </c>
+      <c r="F13" s="48" t="s">
         <v>62</v>
-      </c>
-      <c r="D13" s="48" t="s">
-        <v>69</v>
-      </c>
-      <c r="E13" s="48" t="s">
-        <v>74</v>
-      </c>
-      <c r="F13" s="48" t="s">
-        <v>63</v>
       </c>
       <c r="G13" s="47">
         <v>5</v>
       </c>
       <c r="H13" s="48" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="I13" s="47">
         <v>3</v>
@@ -11090,33 +11053,33 @@
         <v>1</v>
       </c>
       <c r="L13" s="48" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
     </row>
     <row r="14" spans="1:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="45" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="B14" s="46" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C14" s="46" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D14" s="46" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E14" s="46" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="F14" s="46" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="G14" s="45">
         <v>4</v>
       </c>
       <c r="H14" s="46" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="I14" s="45">
         <v>4</v>
@@ -11128,33 +11091,33 @@
         <v>2</v>
       </c>
       <c r="L14" s="46" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
     </row>
     <row r="15" spans="1:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="47" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="B15" s="48" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C15" s="48" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D15" s="48" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="E15" s="48" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="F15" s="48" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="G15" s="47">
         <v>2</v>
       </c>
       <c r="H15" s="48" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="I15" s="47">
         <v>5</v>
@@ -11166,33 +11129,33 @@
         <v>1</v>
       </c>
       <c r="L15" s="48" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
     </row>
     <row r="16" spans="1:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="45" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="B16" s="46" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C16" s="46" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D16" s="46" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E16" s="46" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="F16" s="46" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="G16" s="45">
         <v>4</v>
       </c>
       <c r="H16" s="46" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="I16" s="45">
         <v>5</v>
@@ -11204,33 +11167,33 @@
         <v>1</v>
       </c>
       <c r="L16" s="46" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
     </row>
     <row r="17" spans="1:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="47" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="B17" s="48" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C17" s="48" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D17" s="48" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E17" s="48" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="F17" s="48" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="G17" s="47">
         <v>3</v>
       </c>
       <c r="H17" s="48" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="I17" s="47">
         <v>4</v>
@@ -11242,33 +11205,33 @@
         <v>3</v>
       </c>
       <c r="L17" s="48" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
     </row>
     <row r="18" spans="1:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="45" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="B18" s="46" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C18" s="46" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D18" s="46" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E18" s="46" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="F18" s="46" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="G18" s="45">
         <v>3</v>
       </c>
       <c r="H18" s="46" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="I18" s="45">
         <v>2</v>
@@ -11280,33 +11243,33 @@
         <v>5</v>
       </c>
       <c r="L18" s="46" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="19" spans="1:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="47" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="B19" s="48" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C19" s="48" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D19" s="48" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E19" s="48" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="F19" s="48" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="G19" s="47">
         <v>4</v>
       </c>
       <c r="H19" s="48" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="I19" s="47">
         <v>5</v>
@@ -11318,33 +11281,33 @@
         <v>4</v>
       </c>
       <c r="L19" s="48" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
     </row>
     <row r="20" spans="1:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="45" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="B20" s="46" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C20" s="46" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D20" s="46" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E20" s="46" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="F20" s="46" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="G20" s="45">
         <v>3</v>
       </c>
       <c r="H20" s="46" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="I20" s="45">
         <v>3</v>
@@ -11356,33 +11319,33 @@
         <v>1</v>
       </c>
       <c r="L20" s="46" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="21" spans="1:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="47" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="B21" s="48" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C21" s="48" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D21" s="48" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E21" s="48" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="F21" s="48" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="G21" s="47">
         <v>5</v>
       </c>
       <c r="H21" s="48" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="I21" s="47">
         <v>4</v>
@@ -11394,33 +11357,33 @@
         <v>2</v>
       </c>
       <c r="L21" s="48" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
     </row>
     <row r="22" spans="1:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="45" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="B22" s="46" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C22" s="46" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D22" s="46" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="E22" s="46" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="F22" s="46" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="G22" s="45">
         <v>2</v>
       </c>
       <c r="H22" s="46" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="I22" s="45">
         <v>5</v>
@@ -11432,33 +11395,33 @@
         <v>4</v>
       </c>
       <c r="L22" s="46" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="23" spans="1:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="47" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="B23" s="48" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C23" s="48" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D23" s="48" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E23" s="48" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="F23" s="48" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="G23" s="47">
         <v>3</v>
       </c>
       <c r="H23" s="48" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="I23" s="47">
         <v>4</v>
@@ -11470,33 +11433,33 @@
         <v>2</v>
       </c>
       <c r="L23" s="48" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
     </row>
     <row r="24" spans="1:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="45" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="B24" s="46" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C24" s="46" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D24" s="46" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E24" s="46" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="F24" s="46" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="G24" s="45">
         <v>5</v>
       </c>
       <c r="H24" s="46" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="I24" s="45">
         <v>4</v>
@@ -11508,33 +11471,33 @@
         <v>4</v>
       </c>
       <c r="L24" s="46" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="25" spans="1:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="47" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="B25" s="48" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C25" s="48" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D25" s="48" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E25" s="48" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="F25" s="48" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="G25" s="47">
         <v>3</v>
       </c>
       <c r="H25" s="48" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="I25" s="47">
         <v>1</v>
@@ -11546,33 +11509,33 @@
         <v>2</v>
       </c>
       <c r="L25" s="48" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
     </row>
     <row r="26" spans="1:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="45" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="B26" s="46" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C26" s="46" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D26" s="46" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E26" s="46" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="F26" s="46" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="G26" s="45">
         <v>3</v>
       </c>
       <c r="H26" s="46" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="I26" s="45">
         <v>5</v>
@@ -11584,33 +11547,33 @@
         <v>5</v>
       </c>
       <c r="L26" s="46" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="27" spans="1:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="47" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="B27" s="48" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C27" s="48" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D27" s="48" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E27" s="48" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="F27" s="48" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="G27" s="47">
         <v>4</v>
       </c>
       <c r="H27" s="48" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="I27" s="47">
         <v>5</v>
@@ -11622,33 +11585,33 @@
         <v>3</v>
       </c>
       <c r="L27" s="48" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
     </row>
     <row r="28" spans="1:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="45" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="B28" s="46" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C28" s="46" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D28" s="46" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="E28" s="46" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="F28" s="46" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="G28" s="45">
         <v>5</v>
       </c>
       <c r="H28" s="46" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="I28" s="45">
         <v>5</v>
@@ -11660,33 +11623,33 @@
         <v>5</v>
       </c>
       <c r="L28" s="46" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
     </row>
     <row r="29" spans="1:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="47" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="B29" s="48" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C29" s="48" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D29" s="48" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="E29" s="48" t="s">
+        <v>73</v>
+      </c>
+      <c r="F29" s="48" t="s">
         <v>74</v>
-      </c>
-      <c r="F29" s="48" t="s">
-        <v>75</v>
       </c>
       <c r="G29" s="47">
         <v>4</v>
       </c>
       <c r="H29" s="48" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="I29" s="47">
         <v>3</v>
@@ -11698,33 +11661,33 @@
         <v>4</v>
       </c>
       <c r="L29" s="48" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
     </row>
     <row r="30" spans="1:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="45" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="B30" s="46" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C30" s="46" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D30" s="46" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E30" s="46" t="s">
+        <v>73</v>
+      </c>
+      <c r="F30" s="46" t="s">
         <v>74</v>
-      </c>
-      <c r="F30" s="46" t="s">
-        <v>75</v>
       </c>
       <c r="G30" s="45">
         <v>3</v>
       </c>
       <c r="H30" s="46" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="I30" s="45">
         <v>5</v>
@@ -11736,33 +11699,33 @@
         <v>3</v>
       </c>
       <c r="L30" s="46" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
     </row>
     <row r="31" spans="1:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="47" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="B31" s="48" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C31" s="48" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D31" s="48" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E31" s="48" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="F31" s="48" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="G31" s="47">
         <v>3</v>
       </c>
       <c r="H31" s="48" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="I31" s="47">
         <v>3</v>
@@ -11774,7 +11737,7 @@
         <v>3</v>
       </c>
       <c r="L31" s="48" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
     </row>
   </sheetData>
@@ -11850,60 +11813,60 @@
   <sheetData>
     <row r="1" spans="1:12" ht="86.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="49" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="B1" s="49" t="s">
+        <v>213</v>
+      </c>
+      <c r="C1" s="49" t="s">
         <v>214</v>
       </c>
-      <c r="C1" s="49" t="s">
+      <c r="D1" s="49" t="s">
         <v>215</v>
       </c>
-      <c r="D1" s="49" t="s">
+      <c r="E1" s="49" t="s">
         <v>216</v>
       </c>
-      <c r="E1" s="49" t="s">
+      <c r="F1" s="49" t="s">
         <v>217</v>
       </c>
-      <c r="F1" s="49" t="s">
+      <c r="G1" s="49" t="s">
         <v>218</v>
       </c>
-      <c r="G1" s="49" t="s">
+      <c r="H1" s="49" t="s">
         <v>219</v>
       </c>
-      <c r="H1" s="49" t="s">
+      <c r="I1" s="49" t="s">
         <v>220</v>
       </c>
-      <c r="I1" s="49" t="s">
+      <c r="J1" s="49" t="s">
         <v>221</v>
       </c>
-      <c r="J1" s="49" t="s">
+      <c r="K1" s="49" t="s">
         <v>222</v>
       </c>
-      <c r="K1" s="49" t="s">
+      <c r="L1" s="49" t="s">
         <v>223</v>
-      </c>
-      <c r="L1" s="49" t="s">
-        <v>224</v>
       </c>
     </row>
     <row r="2" spans="1:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="45" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="B2" s="46" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C2" s="46" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D2" s="45">
         <v>29</v>
       </c>
       <c r="E2" s="46" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="F2" s="46" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="G2" s="45">
         <v>5</v>
@@ -11921,27 +11884,27 @@
         <v>4</v>
       </c>
       <c r="L2" s="46" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
     </row>
     <row r="3" spans="1:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="47" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="B3" s="48" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C3" s="48" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D3" s="47">
         <v>23</v>
       </c>
       <c r="E3" s="48" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="F3" s="48" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="G3" s="47">
         <v>4</v>
@@ -11959,27 +11922,27 @@
         <v>3</v>
       </c>
       <c r="L3" s="48" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
     </row>
     <row r="4" spans="1:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="45" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="B4" s="46" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C4" s="46" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D4" s="45">
         <v>26</v>
       </c>
       <c r="E4" s="46" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="F4" s="46" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="G4" s="45">
         <v>3</v>
@@ -11997,27 +11960,27 @@
         <v>4</v>
       </c>
       <c r="L4" s="46" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
     </row>
     <row r="5" spans="1:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="47" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="B5" s="48" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C5" s="48" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D5" s="47">
         <v>19</v>
       </c>
       <c r="E5" s="48" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="F5" s="48" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="G5" s="47">
         <v>4</v>
@@ -12035,27 +11998,27 @@
         <v>3</v>
       </c>
       <c r="L5" s="48" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
     </row>
     <row r="6" spans="1:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="45" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="B6" s="46" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C6" s="46" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D6" s="45">
         <v>21</v>
       </c>
       <c r="E6" s="46" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="F6" s="46" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="G6" s="45">
         <v>4</v>
@@ -12073,27 +12036,27 @@
         <v>5</v>
       </c>
       <c r="L6" s="46" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
     </row>
     <row r="7" spans="1:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="47" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="B7" s="48" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C7" s="48" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D7" s="47">
         <v>22</v>
       </c>
       <c r="E7" s="48" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="F7" s="48" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="G7" s="47">
         <v>3</v>
@@ -12111,27 +12074,27 @@
         <v>4</v>
       </c>
       <c r="L7" s="48" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
     </row>
     <row r="8" spans="1:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="45" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="B8" s="46" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C8" s="46" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D8" s="45">
         <v>25</v>
       </c>
       <c r="E8" s="46" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="F8" s="46" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="G8" s="45">
         <v>4</v>
@@ -12149,27 +12112,27 @@
         <v>2</v>
       </c>
       <c r="L8" s="46" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
     </row>
     <row r="9" spans="1:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="47" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="B9" s="48" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C9" s="48" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D9" s="47">
         <v>13</v>
       </c>
       <c r="E9" s="48" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="F9" s="48" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="G9" s="47">
         <v>5</v>
@@ -12187,7 +12150,7 @@
         <v>3</v>
       </c>
       <c r="L9" s="48" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
     </row>
   </sheetData>
@@ -12264,48 +12227,48 @@
   <sheetData>
     <row r="1" spans="1:11" ht="86.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="50" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="B1" s="50" t="s">
+        <v>236</v>
+      </c>
+      <c r="C1" s="50" t="s">
         <v>237</v>
       </c>
-      <c r="C1" s="50" t="s">
+      <c r="D1" s="50" t="s">
         <v>238</v>
       </c>
-      <c r="D1" s="50" t="s">
+      <c r="E1" s="50" t="s">
         <v>239</v>
       </c>
-      <c r="E1" s="50" t="s">
+      <c r="F1" s="50" t="s">
         <v>240</v>
       </c>
-      <c r="F1" s="50" t="s">
+      <c r="G1" s="50" t="s">
         <v>241</v>
       </c>
-      <c r="G1" s="50" t="s">
+      <c r="H1" s="50" t="s">
         <v>242</v>
       </c>
-      <c r="H1" s="50" t="s">
+      <c r="I1" s="50" t="s">
         <v>243</v>
       </c>
-      <c r="I1" s="50" t="s">
+      <c r="J1" s="50" t="s">
         <v>244</v>
       </c>
-      <c r="J1" s="50" t="s">
+      <c r="K1" s="50" t="s">
         <v>245</v>
-      </c>
-      <c r="K1" s="50" t="s">
-        <v>246</v>
       </c>
     </row>
     <row r="2" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="45" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="B2" s="46" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="C2" s="46" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="D2" s="45">
         <v>2</v>
@@ -12314,10 +12277,10 @@
         <v>32</v>
       </c>
       <c r="F2" s="46" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="G2" s="46" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="H2" s="45">
         <v>5</v>
@@ -12326,21 +12289,21 @@
         <v>5</v>
       </c>
       <c r="J2" s="46" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="K2" s="46" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
     </row>
     <row r="3" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="47" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="B3" s="48" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C3" s="48" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="D3" s="47">
         <v>1</v>
@@ -12349,10 +12312,10 @@
         <v>37</v>
       </c>
       <c r="F3" s="48" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="G3" s="48" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="H3" s="47">
         <v>5</v>
@@ -12361,21 +12324,21 @@
         <v>5</v>
       </c>
       <c r="J3" s="48" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="K3" s="48" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
     </row>
     <row r="4" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="45" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="B4" s="46" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="C4" s="46" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="D4" s="45">
         <v>4</v>
@@ -12384,10 +12347,10 @@
         <v>15</v>
       </c>
       <c r="F4" s="46" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="G4" s="46" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="H4" s="45">
         <v>4</v>
@@ -12396,21 +12359,21 @@
         <v>1</v>
       </c>
       <c r="J4" s="46" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="K4" s="46" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
     </row>
     <row r="5" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="47" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="B5" s="48" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="C5" s="48" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="D5" s="47">
         <v>2</v>
@@ -12419,10 +12382,10 @@
         <v>43</v>
       </c>
       <c r="F5" s="48" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="G5" s="48" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="H5" s="47">
         <v>4</v>
@@ -12431,21 +12394,21 @@
         <v>5</v>
       </c>
       <c r="J5" s="48" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="K5" s="48" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
     </row>
     <row r="6" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="45" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="B6" s="46" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C6" s="46" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="D6" s="45">
         <v>2</v>
@@ -12454,10 +12417,10 @@
         <v>19</v>
       </c>
       <c r="F6" s="46" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="G6" s="46" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="H6" s="45">
         <v>5</v>
@@ -12466,21 +12429,21 @@
         <v>3</v>
       </c>
       <c r="J6" s="46" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="K6" s="46" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
     </row>
     <row r="7" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="47" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="B7" s="48" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="C7" s="48" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="D7" s="47">
         <v>2</v>
@@ -12489,10 +12452,10 @@
         <v>42</v>
       </c>
       <c r="F7" s="48" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="G7" s="48" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="H7" s="47">
         <v>4</v>
@@ -12501,10 +12464,10 @@
         <v>4</v>
       </c>
       <c r="J7" s="48" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="K7" s="48" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
     </row>
   </sheetData>
